--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2046,8 +2046,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="169" formatCode="[$INR]\ #,##0.00"/>
-    <numFmt numFmtId="174" formatCode="[$₹-44E]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="[$INR]\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$₹-44E]#,##0.00"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -2583,7 +2583,7 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2593,7 +2593,7 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="40% - Accent4" xfId="3" builtinId="43"/>

--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omsup\Documents\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD47E01-2010-41ED-9F0C-E7C9A752FB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFF2CC8-D5BE-42E2-801F-C051CD4465F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cond_formatting" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="if_else" sheetId="7" r:id="rId5"/>
     <sheet name="Advanced_functions" sheetId="8" r:id="rId6"/>
     <sheet name="Sheet2" sheetId="9" r:id="rId7"/>
+    <sheet name="Lookup_func" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet2!$C$15:$C$24</definedName>
@@ -39,7 +40,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4698" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4722" uniqueCount="693">
   <si>
     <t>Region</t>
   </si>
@@ -2126,6 +2127,27 @@
   </si>
   <si>
     <t>total sales subtotal</t>
+  </si>
+  <si>
+    <t>EmpID</t>
+  </si>
+  <si>
+    <t>Employee_ID</t>
+  </si>
+  <si>
+    <t>row</t>
+  </si>
+  <si>
+    <t>column</t>
+  </si>
+  <si>
+    <t>Using vookup</t>
+  </si>
+  <si>
+    <t>Using Index Match</t>
+  </si>
+  <si>
+    <t>index-match</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2157,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="[$INR]\ #,##0.00"/>
-    <numFmt numFmtId="170" formatCode="[$₹-439]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$₹-439]#,##0.00"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -2292,7 +2314,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2341,8 +2363,26 @@
         <bgColor indexed="24"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2533,6 +2573,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2540,7 +2591,7 @@
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2689,12 +2740,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2702,6 +2750,27 @@
     <xf numFmtId="164" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="40% - Accent4" xfId="3" builtinId="43"/>
@@ -2709,7 +2778,46 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6600FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2734,6 +2842,33 @@
           <color theme="1"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2775,6 +2910,35 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
@@ -2790,6 +2954,35 @@
           <color theme="1"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2832,16 +3025,17 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2884,6 +3078,33 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
@@ -2894,6 +3115,86 @@
           <color theme="1"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2937,17 +3238,18 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thin">
           <color theme="1"/>
         </top>
         <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2991,7 +3293,115 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -3044,9 +3454,9 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3073,601 +3483,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF6600FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF6600FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF6600FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF6600FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF6600FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -3718,6 +3533,32 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3729,6 +3570,32 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3772,6 +3639,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3799,6 +3692,32 @@
         <sz val="11"/>
         <color theme="1"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
         <scheme val="none"/>
       </font>
       <border diagonalUp="0" diagonalDown="0">
@@ -3810,6 +3729,34 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3920,38 +3867,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{28BA5535-5788-4AB1-921A-039F14F54D15}" name="Table3" displayName="Table3" ref="A1:R500" totalsRowCount="1" headerRowDxfId="61" dataDxfId="60" tableBorderDxfId="59">
-  <autoFilter ref="A1:R499" xr:uid="{28BA5535-5788-4AB1-921A-039F14F54D15}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="North"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{28BA5535-5788-4AB1-921A-039F14F54D15}" name="Table3" displayName="Table3" ref="A1:R500" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
+  <autoFilter ref="A1:R499" xr:uid="{28BA5535-5788-4AB1-921A-039F14F54D15}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q499">
-    <sortCondition sortBy="cellColor" ref="E1:E499" dxfId="58"/>
+    <sortCondition sortBy="cellColor" ref="E1:E499" dxfId="41"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{65E6CC84-6F4C-44CA-9C99-120FD23566F9}" name="Order_ID" dataDxfId="57" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{95D805C7-3A69-4431-813C-AED81C05B129}" name="Region" dataDxfId="56" totalsRowDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{4891D56D-8ABF-4FA3-B907-382919F05DFB}" name="Updated_Region" dataDxfId="55" totalsRowDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{AD731D64-0C98-4E2C-8C7E-DA1C59744960}" name="Category" totalsRowLabel="total sales" dataDxfId="54" totalsRowDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{E3DB0743-D046-45B3-B885-2F62C83EF45F}" name="sales" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{A17DAFFE-BE88-46AE-92E8-5070A02CD175}" name="sales_category" dataDxfId="52" totalsRowDxfId="12">
+    <tableColumn id="1" xr3:uid="{65E6CC84-6F4C-44CA-9C99-120FD23566F9}" name="Order_ID" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{95D805C7-3A69-4431-813C-AED81C05B129}" name="Region" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="17" xr3:uid="{4891D56D-8ABF-4FA3-B907-382919F05DFB}" name="Updated_Region" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{AD731D64-0C98-4E2C-8C7E-DA1C59744960}" name="Category" totalsRowLabel="total sales" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{E3DB0743-D046-45B3-B885-2F62C83EF45F}" name="sales" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{A17DAFFE-BE88-46AE-92E8-5070A02CD175}" name="sales_category" dataDxfId="30" totalsRowDxfId="29">
       <calculatedColumnFormula>IF(Table3[[#This Row],[sales]]&gt;3000,"High Sales",IF(Table3[[#This Row],[sales]]&gt;1000,"Medium Sales",IF(Table3[[#This Row],[sales]]&lt;1000,"Low Sales")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{764C9B79-25BD-4E91-84F1-EF01A46B6CE6}" name="discount" dataDxfId="51" totalsRowDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{8A685D1E-193F-4B06-AEEC-D7B5707356CB}" name="quantity" dataDxfId="50" totalsRowDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{AA2D0404-3A02-492B-A7F9-FB21C0D90029}" name="order_date" dataDxfId="49" totalsRowDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{B84E34D0-E873-4CB7-855D-B95A06454F09}" name="delivery_date" dataDxfId="48" totalsRowDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{02F2D684-13B5-466E-9E84-259BC9E24A6E}" name="Column1" dataDxfId="39" totalsRowDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{67E60644-68E7-461D-89FD-19FEDFE92E33}" name="customer_type" dataDxfId="47" totalsRowDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{DE3BFD9A-B1E4-466F-ABF6-89CAE2992356}" name="customer_type2" dataDxfId="46" totalsRowDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{B560B7F1-8234-4E8A-A0B3-6FAA6B4550A0}" name="payment_mode" dataDxfId="45" totalsRowDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{DB9E1769-0689-4C49-95C9-88E2EF737695}" name="profit" dataDxfId="44" totalsRowDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{C8C418C5-247E-47D9-A677-4A5BAF3FB5B7}" name="city" dataDxfId="43" totalsRowDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{902D2CA8-6521-4B0D-B616-7AFBC6823689}" name="updated_city" dataDxfId="42" totalsRowDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{52801663-005F-401D-B9DE-7B6472E40B55}" name="Discount_category" dataDxfId="41" totalsRowDxfId="0">
+    <tableColumn id="5" xr3:uid="{764C9B79-25BD-4E91-84F1-EF01A46B6CE6}" name="discount" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{8A685D1E-193F-4B06-AEEC-D7B5707356CB}" name="quantity" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{AA2D0404-3A02-492B-A7F9-FB21C0D90029}" name="order_date" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{B84E34D0-E873-4CB7-855D-B95A06454F09}" name="delivery_date" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{02F2D684-13B5-466E-9E84-259BC9E24A6E}" name="Column1" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{67E60644-68E7-461D-89FD-19FEDFE92E33}" name="customer_type" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{DE3BFD9A-B1E4-466F-ABF6-89CAE2992356}" name="customer_type2" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{B560B7F1-8234-4E8A-A0B3-6FAA6B4550A0}" name="payment_mode" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{DB9E1769-0689-4C49-95C9-88E2EF737695}" name="profit" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{C8C418C5-247E-47D9-A677-4A5BAF3FB5B7}" name="city" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{902D2CA8-6521-4B0D-B616-7AFBC6823689}" name="updated_city" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{52801663-005F-401D-B9DE-7B6472E40B55}" name="Discount_category" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>IF(AND(Table3[[#This Row],[customer_type2]]="Member",OR(Table3[[#This Row],[payment_mode]]="UPI",Table3[[#This Row],[payment_mode]]="Card")),"yes","no")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4248,7 +4189,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>147</v>
       </c>
@@ -4316,7 +4257,7 @@
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
     </row>
-    <row r="3" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>208</v>
       </c>
@@ -4383,7 +4324,7 @@
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
     </row>
-    <row r="4" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>119</v>
       </c>
@@ -4450,7 +4391,7 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>311</v>
       </c>
@@ -4517,7 +4458,7 @@
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
     </row>
-    <row r="6" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>431</v>
       </c>
@@ -4586,7 +4527,7 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
-    <row r="7" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>316</v>
       </c>
@@ -4653,7 +4594,7 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>55</v>
       </c>
@@ -4722,7 +4663,7 @@
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
     </row>
-    <row r="9" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>531</v>
       </c>
@@ -4789,7 +4730,7 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>150</v>
       </c>
@@ -4856,7 +4797,7 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>39</v>
       </c>
@@ -4993,7 +4934,7 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
-    <row r="13" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>519</v>
       </c>
@@ -5199,7 +5140,7 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>183</v>
       </c>
@@ -5333,7 +5274,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>387</v>
       </c>
@@ -5402,7 +5343,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>459</v>
       </c>
@@ -5472,7 +5413,7 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>68</v>
       </c>
@@ -5539,7 +5480,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>495</v>
       </c>
@@ -5606,7 +5547,7 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>511</v>
       </c>
@@ -5869,7 +5810,7 @@
       <c r="U25" s="72" t="s">
         <v>655</v>
       </c>
-      <c r="V25" s="75">
+      <c r="V25" s="74">
         <f>SUMIFS(Table3[sales],Table3[Category],"Clothing",Table3[Updated_Region],"east")</f>
         <v>60655.86</v>
       </c>
@@ -5946,7 +5887,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>11</v>
       </c>
@@ -6008,7 +5949,7 @@
       <c r="U27" s="72" t="s">
         <v>667</v>
       </c>
-      <c r="V27" s="75">
+      <c r="V27" s="74">
         <f>SUMIFS(Table3[sales],Table3[Category],"=electronics",Table3[Updated_Region],"=North",Table3[discount],"&gt;40%")</f>
         <v>36091.269999999997</v>
       </c>
@@ -6018,7 +5959,7 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>539</v>
       </c>
@@ -6157,7 +6098,7 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>323</v>
       </c>
@@ -6368,7 +6309,7 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>251</v>
       </c>
@@ -6507,7 +6448,7 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>93</v>
       </c>
@@ -6579,7 +6520,7 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>451</v>
       </c>
@@ -6718,7 +6659,7 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>407</v>
       </c>
@@ -6790,7 +6731,7 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>303</v>
       </c>
@@ -6862,7 +6803,7 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>203</v>
       </c>
@@ -6934,7 +6875,7 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>403</v>
       </c>
@@ -7001,7 +6942,7 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>279</v>
       </c>
@@ -7073,7 +7014,7 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>363</v>
       </c>
@@ -7140,7 +7081,7 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>207</v>
       </c>
@@ -7199,10 +7140,10 @@
       </c>
       <c r="S44" s="1"/>
       <c r="T44" s="1"/>
-      <c r="U44" s="74" t="s">
+      <c r="U44" s="73" t="s">
         <v>668</v>
       </c>
-      <c r="V44" s="75">
+      <c r="V44" s="74">
         <f>SUMIF(Table3[Updated_Region],"North",Table3[sales])</f>
         <v>334964.15999999997</v>
       </c>
@@ -7271,10 +7212,10 @@
       </c>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
-      <c r="U45" s="74" t="s">
+      <c r="U45" s="73" t="s">
         <v>669</v>
       </c>
-      <c r="V45" s="75">
+      <c r="V45" s="74">
         <f>SUMIF(Table3[Updated_Region],"South",Table3[sales])</f>
         <v>303623.69</v>
       </c>
@@ -7343,10 +7284,10 @@
       </c>
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
-      <c r="U46" s="76" t="s">
+      <c r="U46" s="72" t="s">
         <v>670</v>
       </c>
-      <c r="V46" s="75">
+      <c r="V46" s="74">
         <f>SUMIF(Table3[Updated_Region],"East",Table3[sales])</f>
         <v>337881.27000000008</v>
       </c>
@@ -7356,7 +7297,7 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
     </row>
-    <row r="47" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>327</v>
       </c>
@@ -7415,10 +7356,10 @@
       </c>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
-      <c r="U47" s="76" t="s">
+      <c r="U47" s="72" t="s">
         <v>671</v>
       </c>
-      <c r="V47" s="75">
+      <c r="V47" s="74">
         <f>SUMIF(Table3[Updated_Region],"West",Table3[sales])</f>
         <v>346200.06999999989</v>
       </c>
@@ -7428,7 +7369,7 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
     </row>
-    <row r="48" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>171</v>
       </c>
@@ -7554,7 +7495,7 @@
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
-      <c r="U49" s="76" t="s">
+      <c r="U49" s="72" t="s">
         <v>672</v>
       </c>
       <c r="V49" s="73">
@@ -7567,7 +7508,7 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
     </row>
-    <row r="50" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>255</v>
       </c>
@@ -7626,7 +7567,7 @@
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
-      <c r="U50" s="76" t="s">
+      <c r="U50" s="72" t="s">
         <v>673</v>
       </c>
       <c r="V50" s="73">
@@ -7639,7 +7580,7 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
     </row>
-    <row r="51" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>447</v>
       </c>
@@ -7698,7 +7639,7 @@
       </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
-      <c r="U51" s="76" t="s">
+      <c r="U51" s="72" t="s">
         <v>674</v>
       </c>
       <c r="V51" s="73">
@@ -7711,7 +7652,7 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
     </row>
-    <row r="52" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>195</v>
       </c>
@@ -7770,7 +7711,7 @@
       </c>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
-      <c r="U52" s="76" t="s">
+      <c r="U52" s="72" t="s">
         <v>675</v>
       </c>
       <c r="V52" s="73">
@@ -7850,7 +7791,7 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
     </row>
-    <row r="54" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>467</v>
       </c>
@@ -7917,7 +7858,7 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
     </row>
-    <row r="55" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>419</v>
       </c>
@@ -7976,7 +7917,7 @@
       </c>
       <c r="S55" s="1"/>
       <c r="T55" s="1"/>
-      <c r="U55" s="76" t="s">
+      <c r="U55" s="72" t="s">
         <v>676</v>
       </c>
       <c r="V55" s="73">
@@ -7989,7 +7930,7 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
     </row>
-    <row r="56" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>72</v>
       </c>
@@ -8118,7 +8059,7 @@
       <c r="U57" s="72" t="s">
         <v>678</v>
       </c>
-      <c r="V57" s="77">
+      <c r="V57" s="75">
         <f>MAX(Table3[order_date])</f>
         <v>45657</v>
       </c>
@@ -8195,7 +8136,7 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>243</v>
       </c>
@@ -8339,7 +8280,7 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
-    <row r="61" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>239</v>
       </c>
@@ -8670,7 +8611,7 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
     </row>
-    <row r="66" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
         <v>223</v>
       </c>
@@ -8737,7 +8678,7 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
     </row>
-    <row r="67" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>191</v>
       </c>
@@ -8871,7 +8812,7 @@
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
     </row>
-    <row r="69" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>339</v>
       </c>
@@ -9005,7 +8946,7 @@
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
     </row>
-    <row r="71" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>491</v>
       </c>
@@ -9072,7 +9013,7 @@
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
     </row>
-    <row r="72" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
         <v>507</v>
       </c>
@@ -9139,7 +9080,7 @@
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
     </row>
-    <row r="73" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>427</v>
       </c>
@@ -9273,7 +9214,7 @@
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
     </row>
-    <row r="75" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>343</v>
       </c>
@@ -9340,7 +9281,7 @@
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
     </row>
-    <row r="76" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
         <v>479</v>
       </c>
@@ -9474,7 +9415,7 @@
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
     </row>
-    <row r="78" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
         <v>315</v>
       </c>
@@ -9608,7 +9549,7 @@
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
     </row>
-    <row r="80" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
         <v>143</v>
       </c>
@@ -9742,7 +9683,7 @@
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
     </row>
-    <row r="82" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
         <v>331</v>
       </c>
@@ -10077,7 +10018,7 @@
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
     </row>
-    <row r="87" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>267</v>
       </c>
@@ -10211,7 +10152,7 @@
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
     </row>
-    <row r="89" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>335</v>
       </c>
@@ -10546,7 +10487,7 @@
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
     </row>
-    <row r="94" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>395</v>
       </c>
@@ -10814,7 +10755,7 @@
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
     </row>
-    <row r="98" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>411</v>
       </c>
@@ -10948,7 +10889,7 @@
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
     </row>
-    <row r="100" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>85</v>
       </c>
@@ -11015,7 +10956,7 @@
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
     </row>
-    <row r="101" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>415</v>
       </c>
@@ -11082,7 +11023,7 @@
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
     </row>
-    <row r="102" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>187</v>
       </c>
@@ -11149,7 +11090,7 @@
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
     </row>
-    <row r="103" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>76</v>
       </c>
@@ -11216,7 +11157,7 @@
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
     </row>
-    <row r="104" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
         <v>98</v>
       </c>
@@ -11350,7 +11291,7 @@
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
     </row>
-    <row r="106" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
         <v>455</v>
       </c>
@@ -11551,7 +11492,7 @@
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
     </row>
-    <row r="109" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>399</v>
       </c>
@@ -11685,7 +11626,7 @@
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
     </row>
-    <row r="111" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
         <v>227</v>
       </c>
@@ -11819,7 +11760,7 @@
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
     </row>
-    <row r="113" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>487</v>
       </c>
@@ -11886,7 +11827,7 @@
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
     </row>
-    <row r="114" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>271</v>
       </c>
@@ -11953,7 +11894,7 @@
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
     </row>
-    <row r="115" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
         <v>355</v>
       </c>
@@ -12020,7 +11961,7 @@
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
     </row>
-    <row r="116" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
         <v>367</v>
       </c>
@@ -12154,7 +12095,7 @@
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
     </row>
-    <row r="118" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>219</v>
       </c>
@@ -12422,7 +12363,7 @@
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
     </row>
-    <row r="122" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
         <v>81</v>
       </c>
@@ -12489,7 +12430,7 @@
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
     </row>
-    <row r="123" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
         <v>45</v>
       </c>
@@ -12556,7 +12497,7 @@
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
     </row>
-    <row r="124" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
         <v>307</v>
       </c>
@@ -12623,7 +12564,7 @@
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
     </row>
-    <row r="125" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
         <v>103</v>
       </c>
@@ -12891,7 +12832,7 @@
       <c r="Z128" s="1"/>
       <c r="AA128" s="1"/>
     </row>
-    <row r="129" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="13" t="s">
         <v>247</v>
       </c>
@@ -12958,7 +12899,7 @@
       <c r="Z129" s="1"/>
       <c r="AA129" s="1"/>
     </row>
-    <row r="130" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="13" t="s">
         <v>383</v>
       </c>
@@ -13092,7 +13033,7 @@
       <c r="Z131" s="1"/>
       <c r="AA131" s="1"/>
     </row>
-    <row r="132" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="13" t="s">
         <v>379</v>
       </c>
@@ -13159,7 +13100,7 @@
       <c r="Z132" s="1"/>
       <c r="AA132" s="1"/>
     </row>
-    <row r="133" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="13" t="s">
         <v>423</v>
       </c>
@@ -13293,7 +13234,7 @@
       <c r="Z134" s="1"/>
       <c r="AA134" s="1"/>
     </row>
-    <row r="135" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="13" t="s">
         <v>391</v>
       </c>
@@ -13494,7 +13435,7 @@
       <c r="Z137" s="1"/>
       <c r="AA137" s="1"/>
     </row>
-    <row r="138" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="13" t="s">
         <v>50</v>
       </c>
@@ -13561,7 +13502,7 @@
       <c r="Z138" s="1"/>
       <c r="AA138" s="1"/>
     </row>
-    <row r="139" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="13" t="s">
         <v>235</v>
       </c>
@@ -13695,7 +13636,7 @@
       <c r="Z140" s="1"/>
       <c r="AA140" s="1"/>
     </row>
-    <row r="141" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="13" t="s">
         <v>287</v>
       </c>
@@ -13762,7 +13703,7 @@
       <c r="Z141" s="1"/>
       <c r="AA141" s="1"/>
     </row>
-    <row r="142" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="13" t="s">
         <v>515</v>
       </c>
@@ -13829,7 +13770,7 @@
       <c r="Z142" s="1"/>
       <c r="AA142" s="1"/>
     </row>
-    <row r="143" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="13" t="s">
         <v>443</v>
       </c>
@@ -13963,7 +13904,7 @@
       <c r="Z144" s="1"/>
       <c r="AA144" s="1"/>
     </row>
-    <row r="145" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
         <v>347</v>
       </c>
@@ -14030,7 +13971,7 @@
       <c r="Z145" s="1"/>
       <c r="AA145" s="1"/>
     </row>
-    <row r="146" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="13" t="s">
         <v>291</v>
       </c>
@@ -14097,7 +14038,7 @@
       <c r="Z146" s="1"/>
       <c r="AA146" s="1"/>
     </row>
-    <row r="147" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="13" t="s">
         <v>435</v>
       </c>
@@ -14298,7 +14239,7 @@
       <c r="Z149" s="1"/>
       <c r="AA149" s="1"/>
     </row>
-    <row r="150" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="13" t="s">
         <v>283</v>
       </c>
@@ -14365,7 +14306,7 @@
       <c r="Z150" s="1"/>
       <c r="AA150" s="1"/>
     </row>
-    <row r="151" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="13" t="s">
         <v>471</v>
       </c>
@@ -14700,7 +14641,7 @@
       <c r="Z155" s="1"/>
       <c r="AA155" s="1"/>
     </row>
-    <row r="156" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="13" t="s">
         <v>167</v>
       </c>
@@ -14901,7 +14842,7 @@
       <c r="Z158" s="1"/>
       <c r="AA158" s="1"/>
     </row>
-    <row r="159" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
         <v>211</v>
       </c>
@@ -15102,7 +15043,7 @@
       <c r="Z161" s="1"/>
       <c r="AA161" s="1"/>
     </row>
-    <row r="162" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="13" t="s">
         <v>175</v>
       </c>
@@ -15169,7 +15110,7 @@
       <c r="Z162" s="1"/>
       <c r="AA162" s="1"/>
     </row>
-    <row r="163" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="13" t="s">
         <v>135</v>
       </c>
@@ -15236,7 +15177,7 @@
       <c r="Z163" s="1"/>
       <c r="AA163" s="1"/>
     </row>
-    <row r="164" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="13" t="s">
         <v>199</v>
       </c>
@@ -15437,7 +15378,7 @@
       <c r="Z166" s="1"/>
       <c r="AA166" s="1"/>
     </row>
-    <row r="167" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="13" t="s">
         <v>275</v>
       </c>
@@ -15839,7 +15780,7 @@
       <c r="Z172" s="1"/>
       <c r="AA172" s="1"/>
     </row>
-    <row r="173" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="13" t="s">
         <v>30</v>
       </c>
@@ -15906,7 +15847,7 @@
       <c r="Z173" s="1"/>
       <c r="AA173" s="1"/>
     </row>
-    <row r="174" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="13" t="s">
         <v>179</v>
       </c>
@@ -16040,7 +15981,7 @@
       <c r="Z175" s="1"/>
       <c r="AA175" s="1"/>
     </row>
-    <row r="176" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="13" t="s">
         <v>127</v>
       </c>
@@ -16442,7 +16383,7 @@
       <c r="Z181" s="1"/>
       <c r="AA181" s="1"/>
     </row>
-    <row r="182" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="13" t="s">
         <v>503</v>
       </c>
@@ -16509,7 +16450,7 @@
       <c r="Z182" s="1"/>
       <c r="AA182" s="1"/>
     </row>
-    <row r="183" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="13" t="s">
         <v>155</v>
       </c>
@@ -16576,7 +16517,7 @@
       <c r="Z183" s="1"/>
       <c r="AA183" s="1"/>
     </row>
-    <row r="184" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="13" t="s">
         <v>56</v>
       </c>
@@ -16643,7 +16584,7 @@
       <c r="Z184" s="1"/>
       <c r="AA184" s="1"/>
     </row>
-    <row r="185" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="13" t="s">
         <v>111</v>
       </c>
@@ -16710,7 +16651,7 @@
       <c r="Z185" s="1"/>
       <c r="AA185" s="1"/>
     </row>
-    <row r="186" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="13" t="s">
         <v>159</v>
       </c>
@@ -16911,7 +16852,7 @@
       <c r="Z188" s="1"/>
       <c r="AA188" s="1"/>
     </row>
-    <row r="189" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="13" t="s">
         <v>535</v>
       </c>
@@ -17045,7 +16986,7 @@
       <c r="Z190" s="1"/>
       <c r="AA190" s="1"/>
     </row>
-    <row r="191" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="13" t="s">
         <v>527</v>
       </c>
@@ -17380,7 +17321,7 @@
       <c r="Z195" s="1"/>
       <c r="AA195" s="1"/>
     </row>
-    <row r="196" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="13" t="s">
         <v>151</v>
       </c>
@@ -17447,7 +17388,7 @@
       <c r="Z196" s="1"/>
       <c r="AA196" s="1"/>
     </row>
-    <row r="197" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="13" t="s">
         <v>263</v>
       </c>
@@ -17581,7 +17522,7 @@
       <c r="Z198" s="1"/>
       <c r="AA198" s="1"/>
     </row>
-    <row r="199" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="13" t="s">
         <v>475</v>
       </c>
@@ -17715,7 +17656,7 @@
       <c r="Z200" s="1"/>
       <c r="AA200" s="1"/>
     </row>
-    <row r="201" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="13" t="s">
         <v>215</v>
       </c>
@@ -17849,7 +17790,7 @@
       <c r="Z202" s="1"/>
       <c r="AA202" s="1"/>
     </row>
-    <row r="203" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="13" t="s">
         <v>295</v>
       </c>
@@ -17916,7 +17857,7 @@
       <c r="Z203" s="1"/>
       <c r="AA203" s="1"/>
     </row>
-    <row r="204" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="13" t="s">
         <v>319</v>
       </c>
@@ -18050,7 +17991,7 @@
       <c r="Z205" s="1"/>
       <c r="AA205" s="1"/>
     </row>
-    <row r="206" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="13" t="s">
         <v>163</v>
       </c>
@@ -18184,7 +18125,7 @@
       <c r="Z207" s="1"/>
       <c r="AA207" s="1"/>
     </row>
-    <row r="208" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="13" t="s">
         <v>439</v>
       </c>
@@ -18251,7 +18192,7 @@
       <c r="Z208" s="1"/>
       <c r="AA208" s="1"/>
     </row>
-    <row r="209" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="13" t="s">
         <v>523</v>
       </c>
@@ -18787,7 +18728,7 @@
       <c r="Z216" s="1"/>
       <c r="AA216" s="1"/>
     </row>
-    <row r="217" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="13" t="s">
         <v>115</v>
       </c>
@@ -18921,7 +18862,7 @@
       <c r="Z218" s="1"/>
       <c r="AA218" s="1"/>
     </row>
-    <row r="219" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="13" t="s">
         <v>299</v>
       </c>
@@ -19390,7 +19331,7 @@
       <c r="Z225" s="1"/>
       <c r="AA225" s="1"/>
     </row>
-    <row r="226" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="13" t="s">
         <v>483</v>
       </c>
@@ -20060,7 +20001,7 @@
       <c r="Z235" s="1"/>
       <c r="AA235" s="1"/>
     </row>
-    <row r="236" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="13" t="s">
         <v>131</v>
       </c>
@@ -20194,7 +20135,7 @@
       <c r="Z237" s="1"/>
       <c r="AA237" s="1"/>
     </row>
-    <row r="238" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="13" t="s">
         <v>463</v>
       </c>
@@ -20261,7 +20202,7 @@
       <c r="Z238" s="1"/>
       <c r="AA238" s="1"/>
     </row>
-    <row r="239" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="13" t="s">
         <v>351</v>
       </c>
@@ -20328,7 +20269,7 @@
       <c r="Z239" s="1"/>
       <c r="AA239" s="1"/>
     </row>
-    <row r="240" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="13" t="s">
         <v>259</v>
       </c>
@@ -20462,7 +20403,7 @@
       <c r="Z241" s="1"/>
       <c r="AA241" s="1"/>
     </row>
-    <row r="242" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="13" t="s">
         <v>375</v>
       </c>
@@ -20529,7 +20470,7 @@
       <c r="Z242" s="1"/>
       <c r="AA242" s="1"/>
     </row>
-    <row r="243" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="13" t="s">
         <v>371</v>
       </c>
@@ -20596,7 +20537,7 @@
       <c r="Z243" s="1"/>
       <c r="AA243" s="1"/>
     </row>
-    <row r="244" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="13" t="s">
         <v>359</v>
       </c>
@@ -20663,7 +20604,7 @@
       <c r="Z244" s="1"/>
       <c r="AA244" s="1"/>
     </row>
-    <row r="245" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="13" t="s">
         <v>231</v>
       </c>
@@ -20730,7 +20671,7 @@
       <c r="Z245" s="1"/>
       <c r="AA245" s="1"/>
     </row>
-    <row r="246" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="13" t="s">
         <v>499</v>
       </c>
@@ -20864,7 +20805,7 @@
       <c r="Z247" s="1"/>
       <c r="AA247" s="1"/>
     </row>
-    <row r="248" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="13" t="s">
         <v>107</v>
       </c>
@@ -20931,7 +20872,7 @@
       <c r="Z248" s="1"/>
       <c r="AA248" s="1"/>
     </row>
-    <row r="249" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="13" t="s">
         <v>139</v>
       </c>
@@ -20998,7 +20939,7 @@
       <c r="Z249" s="1"/>
       <c r="AA249" s="1"/>
     </row>
-    <row r="250" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="13" t="s">
         <v>61</v>
       </c>
@@ -21065,7 +21006,7 @@
       <c r="Z250" s="1"/>
       <c r="AA250" s="1"/>
     </row>
-    <row r="251" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="13" t="s">
         <v>89</v>
       </c>
@@ -21199,7 +21140,7 @@
       <c r="Z252" s="1"/>
       <c r="AA252" s="1"/>
     </row>
-    <row r="253" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="13" t="s">
         <v>123</v>
       </c>
@@ -21333,7 +21274,7 @@
       <c r="Z254" s="1"/>
       <c r="AA254" s="1"/>
     </row>
-    <row r="255" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="8" t="s">
         <v>344</v>
       </c>
@@ -21400,7 +21341,7 @@
       <c r="Z255" s="1"/>
       <c r="AA255" s="1"/>
     </row>
-    <row r="256" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="8" t="s">
         <v>230</v>
       </c>
@@ -21467,7 +21408,7 @@
       <c r="Z256" s="1"/>
       <c r="AA256" s="1"/>
     </row>
-    <row r="257" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="8" t="s">
         <v>258</v>
       </c>
@@ -21534,7 +21475,7 @@
       <c r="Z257" s="1"/>
       <c r="AA257" s="1"/>
     </row>
-    <row r="258" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="8" t="s">
         <v>358</v>
       </c>
@@ -21601,7 +21542,7 @@
       <c r="Z258" s="1"/>
       <c r="AA258" s="1"/>
     </row>
-    <row r="259" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="8" t="s">
         <v>382</v>
       </c>
@@ -21668,7 +21609,7 @@
       <c r="Z259" s="1"/>
       <c r="AA259" s="1"/>
     </row>
-    <row r="260" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="8" t="s">
         <v>164</v>
       </c>
@@ -21735,7 +21676,7 @@
       <c r="Z260" s="1"/>
       <c r="AA260" s="1"/>
     </row>
-    <row r="261" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="8" t="s">
         <v>95</v>
       </c>
@@ -21802,7 +21743,7 @@
       <c r="Z261" s="1"/>
       <c r="AA261" s="1"/>
     </row>
-    <row r="262" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="8" t="s">
         <v>476</v>
       </c>
@@ -21869,7 +21810,7 @@
       <c r="Z262" s="1"/>
       <c r="AA262" s="1"/>
     </row>
-    <row r="263" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="8" t="s">
         <v>80</v>
       </c>
@@ -21936,7 +21877,7 @@
       <c r="Z263" s="1"/>
       <c r="AA263" s="1"/>
     </row>
-    <row r="264" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="8" t="s">
         <v>102</v>
       </c>
@@ -22003,7 +21944,7 @@
       <c r="Z264" s="1"/>
       <c r="AA264" s="1"/>
     </row>
-    <row r="265" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="8" t="s">
         <v>186</v>
       </c>
@@ -22070,7 +22011,7 @@
       <c r="Z265" s="1"/>
       <c r="AA265" s="1"/>
     </row>
-    <row r="266" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="8" t="s">
         <v>278</v>
       </c>
@@ -22137,7 +22078,7 @@
       <c r="Z266" s="1"/>
       <c r="AA266" s="1"/>
     </row>
-    <row r="267" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="8" t="s">
         <v>41</v>
       </c>
@@ -22204,7 +22145,7 @@
       <c r="Z267" s="1"/>
       <c r="AA267" s="1"/>
     </row>
-    <row r="268" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="8" t="s">
         <v>512</v>
       </c>
@@ -22271,7 +22212,7 @@
       <c r="Z268" s="1"/>
       <c r="AA268" s="1"/>
     </row>
-    <row r="269" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="8" t="s">
         <v>104</v>
       </c>
@@ -22338,7 +22279,7 @@
       <c r="Z269" s="1"/>
       <c r="AA269" s="1"/>
     </row>
-    <row r="270" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="8" t="s">
         <v>126</v>
       </c>
@@ -22405,7 +22346,7 @@
       <c r="Z270" s="1"/>
       <c r="AA270" s="1"/>
     </row>
-    <row r="271" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="8" t="s">
         <v>402</v>
       </c>
@@ -22472,7 +22413,7 @@
       <c r="Z271" s="1"/>
       <c r="AA271" s="1"/>
     </row>
-    <row r="272" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="8" t="s">
         <v>502</v>
       </c>
@@ -22539,7 +22480,7 @@
       <c r="Z272" s="1"/>
       <c r="AA272" s="1"/>
     </row>
-    <row r="273" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="8" t="s">
         <v>75</v>
       </c>
@@ -22606,7 +22547,7 @@
       <c r="Z273" s="1"/>
       <c r="AA273" s="1"/>
     </row>
-    <row r="274" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="8" t="s">
         <v>286</v>
       </c>
@@ -22673,7 +22614,7 @@
       <c r="Z274" s="1"/>
       <c r="AA274" s="1"/>
     </row>
-    <row r="275" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="8" t="s">
         <v>354</v>
       </c>
@@ -22740,7 +22681,7 @@
       <c r="Z275" s="1"/>
       <c r="AA275" s="1"/>
     </row>
-    <row r="276" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="8" t="s">
         <v>366</v>
       </c>
@@ -22807,7 +22748,7 @@
       <c r="Z276" s="1"/>
       <c r="AA276" s="1"/>
     </row>
-    <row r="277" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="8" t="s">
         <v>232</v>
       </c>
@@ -22874,7 +22815,7 @@
       <c r="Z277" s="1"/>
       <c r="AA277" s="1"/>
     </row>
-    <row r="278" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="8" t="s">
         <v>514</v>
       </c>
@@ -22941,7 +22882,7 @@
       <c r="Z278" s="1"/>
       <c r="AA278" s="1"/>
     </row>
-    <row r="279" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="8" t="s">
         <v>154</v>
       </c>
@@ -23008,7 +22949,7 @@
       <c r="Z279" s="1"/>
       <c r="AA279" s="1"/>
     </row>
-    <row r="280" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="8" t="s">
         <v>378</v>
       </c>
@@ -23075,7 +23016,7 @@
       <c r="Z280" s="1"/>
       <c r="AA280" s="1"/>
     </row>
-    <row r="281" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="8" t="s">
         <v>406</v>
       </c>
@@ -23142,7 +23083,7 @@
       <c r="Z281" s="1"/>
       <c r="AA281" s="1"/>
     </row>
-    <row r="282" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="8" t="s">
         <v>220</v>
       </c>
@@ -23209,7 +23150,7 @@
       <c r="Z282" s="1"/>
       <c r="AA282" s="1"/>
     </row>
-    <row r="283" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="8" t="s">
         <v>440</v>
       </c>
@@ -23276,7 +23217,7 @@
       <c r="Z283" s="1"/>
       <c r="AA283" s="1"/>
     </row>
-    <row r="284" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="8" t="s">
         <v>132</v>
       </c>
@@ -23343,7 +23284,7 @@
       <c r="Z284" s="1"/>
       <c r="AA284" s="1"/>
     </row>
-    <row r="285" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="8" t="s">
         <v>352</v>
       </c>
@@ -23410,7 +23351,7 @@
       <c r="Z285" s="1"/>
       <c r="AA285" s="1"/>
     </row>
-    <row r="286" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="8" t="s">
         <v>392</v>
       </c>
@@ -23477,7 +23418,7 @@
       <c r="Z286" s="1"/>
       <c r="AA286" s="1"/>
     </row>
-    <row r="287" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="8" t="s">
         <v>254</v>
       </c>
@@ -23544,7 +23485,7 @@
       <c r="Z287" s="1"/>
       <c r="AA287" s="1"/>
     </row>
-    <row r="288" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="8" t="s">
         <v>530</v>
       </c>
@@ -23611,7 +23552,7 @@
       <c r="Z288" s="1"/>
       <c r="AA288" s="1"/>
     </row>
-    <row r="289" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="8" t="s">
         <v>496</v>
       </c>
@@ -23678,7 +23619,7 @@
       <c r="Z289" s="1"/>
       <c r="AA289" s="1"/>
     </row>
-    <row r="290" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="8" t="s">
         <v>416</v>
       </c>
@@ -23745,7 +23686,7 @@
       <c r="Z290" s="1"/>
       <c r="AA290" s="1"/>
     </row>
-    <row r="291" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="8" t="s">
         <v>236</v>
       </c>
@@ -23812,7 +23753,7 @@
       <c r="Z291" s="1"/>
       <c r="AA291" s="1"/>
     </row>
-    <row r="292" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="8" t="s">
         <v>124</v>
       </c>
@@ -23879,7 +23820,7 @@
       <c r="Z292" s="1"/>
       <c r="AA292" s="1"/>
     </row>
-    <row r="293" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="8" t="s">
         <v>492</v>
       </c>
@@ -23946,7 +23887,7 @@
       <c r="Z293" s="1"/>
       <c r="AA293" s="1"/>
     </row>
-    <row r="294" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="8" t="s">
         <v>106</v>
       </c>
@@ -24013,7 +23954,7 @@
       <c r="Z294" s="1"/>
       <c r="AA294" s="1"/>
     </row>
-    <row r="295" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="8" t="s">
         <v>414</v>
       </c>
@@ -24080,7 +24021,7 @@
       <c r="Z295" s="1"/>
       <c r="AA295" s="1"/>
     </row>
-    <row r="296" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="8" t="s">
         <v>84</v>
       </c>
@@ -24147,7 +24088,7 @@
       <c r="Z296" s="1"/>
       <c r="AA296" s="1"/>
     </row>
-    <row r="297" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="8" t="s">
         <v>494</v>
       </c>
@@ -24214,7 +24155,7 @@
       <c r="Z297" s="1"/>
       <c r="AA297" s="1"/>
     </row>
-    <row r="298" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="8" t="s">
         <v>216</v>
       </c>
@@ -24281,7 +24222,7 @@
       <c r="Z298" s="1"/>
       <c r="AA298" s="1"/>
     </row>
-    <row r="299" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="8" t="s">
         <v>364</v>
       </c>
@@ -24348,7 +24289,7 @@
       <c r="Z299" s="1"/>
       <c r="AA299" s="1"/>
     </row>
-    <row r="300" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="8" t="s">
         <v>284</v>
       </c>
@@ -24415,7 +24356,7 @@
       <c r="Z300" s="1"/>
       <c r="AA300" s="1"/>
     </row>
-    <row r="301" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="8" t="s">
         <v>296</v>
       </c>
@@ -24482,7 +24423,7 @@
       <c r="Z301" s="1"/>
       <c r="AA301" s="1"/>
     </row>
-    <row r="302" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="8" t="s">
         <v>290</v>
       </c>
@@ -24549,7 +24490,7 @@
       <c r="Z302" s="1"/>
       <c r="AA302" s="1"/>
     </row>
-    <row r="303" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="8" t="s">
         <v>534</v>
       </c>
@@ -24616,7 +24557,7 @@
       <c r="Z303" s="1"/>
       <c r="AA303" s="1"/>
     </row>
-    <row r="304" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="8" t="s">
         <v>250</v>
       </c>
@@ -24683,7 +24624,7 @@
       <c r="Z304" s="1"/>
       <c r="AA304" s="1"/>
     </row>
-    <row r="305" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="8" t="s">
         <v>120</v>
       </c>
@@ -24750,7 +24691,7 @@
       <c r="Z305" s="1"/>
       <c r="AA305" s="1"/>
     </row>
-    <row r="306" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="8" t="s">
         <v>526</v>
       </c>
@@ -24817,7 +24758,7 @@
       <c r="Z306" s="1"/>
       <c r="AA306" s="1"/>
     </row>
-    <row r="307" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="8" t="s">
         <v>282</v>
       </c>
@@ -24884,7 +24825,7 @@
       <c r="Z307" s="1"/>
       <c r="AA307" s="1"/>
     </row>
-    <row r="308" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="8" t="s">
         <v>49</v>
       </c>
@@ -24951,7 +24892,7 @@
       <c r="Z308" s="1"/>
       <c r="AA308" s="1"/>
     </row>
-    <row r="309" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="8" t="s">
         <v>356</v>
       </c>
@@ -25018,7 +24959,7 @@
       <c r="Z309" s="1"/>
       <c r="AA309" s="1"/>
     </row>
-    <row r="310" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="8" t="s">
         <v>260</v>
       </c>
@@ -25085,7 +25026,7 @@
       <c r="Z310" s="1"/>
       <c r="AA310" s="1"/>
     </row>
-    <row r="311" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="8" t="s">
         <v>238</v>
       </c>
@@ -25152,7 +25093,7 @@
       <c r="Z311" s="1"/>
       <c r="AA311" s="1"/>
     </row>
-    <row r="312" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="8" t="s">
         <v>226</v>
       </c>
@@ -25219,7 +25160,7 @@
       <c r="Z312" s="1"/>
       <c r="AA312" s="1"/>
     </row>
-    <row r="313" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="8" t="s">
         <v>522</v>
       </c>
@@ -25286,7 +25227,7 @@
       <c r="Z313" s="1"/>
       <c r="AA313" s="1"/>
     </row>
-    <row r="314" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="8" t="s">
         <v>244</v>
       </c>
@@ -25353,7 +25294,7 @@
       <c r="Z314" s="1"/>
       <c r="AA314" s="1"/>
     </row>
-    <row r="315" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="8" t="s">
         <v>334</v>
       </c>
@@ -25420,7 +25361,7 @@
       <c r="Z315" s="1"/>
       <c r="AA315" s="1"/>
     </row>
-    <row r="316" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="8" t="s">
         <v>432</v>
       </c>
@@ -25487,7 +25428,7 @@
       <c r="Z316" s="1"/>
       <c r="AA316" s="1"/>
     </row>
-    <row r="317" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="8" t="s">
         <v>398</v>
       </c>
@@ -25554,7 +25495,7 @@
       <c r="Z317" s="1"/>
       <c r="AA317" s="1"/>
     </row>
-    <row r="318" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="8" t="s">
         <v>450</v>
       </c>
@@ -25621,7 +25562,7 @@
       <c r="Z318" s="1"/>
       <c r="AA318" s="1"/>
     </row>
-    <row r="319" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="8" t="s">
         <v>338</v>
       </c>
@@ -25688,7 +25629,7 @@
       <c r="Z319" s="1"/>
       <c r="AA319" s="1"/>
     </row>
-    <row r="320" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="8" t="s">
         <v>276</v>
       </c>
@@ -25755,7 +25696,7 @@
       <c r="Z320" s="1"/>
       <c r="AA320" s="1"/>
     </row>
-    <row r="321" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="8" t="s">
         <v>178</v>
       </c>
@@ -25822,7 +25763,7 @@
       <c r="Z321" s="1"/>
       <c r="AA321" s="1"/>
     </row>
-    <row r="322" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="8" t="s">
         <v>442</v>
       </c>
@@ -25889,7 +25830,7 @@
       <c r="Z322" s="1"/>
       <c r="AA322" s="1"/>
     </row>
-    <row r="323" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="8" t="s">
         <v>454</v>
       </c>
@@ -25956,7 +25897,7 @@
       <c r="Z323" s="1"/>
       <c r="AA323" s="1"/>
     </row>
-    <row r="324" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="8" t="s">
         <v>27</v>
       </c>
@@ -26023,7 +25964,7 @@
       <c r="Z324" s="1"/>
       <c r="AA324" s="1"/>
     </row>
-    <row r="325" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="8" t="s">
         <v>156</v>
       </c>
@@ -26090,7 +26031,7 @@
       <c r="Z325" s="1"/>
       <c r="AA325" s="1"/>
     </row>
-    <row r="326" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="8" t="s">
         <v>336</v>
       </c>
@@ -26157,7 +26098,7 @@
       <c r="Z326" s="1"/>
       <c r="AA326" s="1"/>
     </row>
-    <row r="327" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="8" t="s">
         <v>328</v>
       </c>
@@ -26224,7 +26165,7 @@
       <c r="Z327" s="1"/>
       <c r="AA327" s="1"/>
     </row>
-    <row r="328" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="8" t="s">
         <v>176</v>
       </c>
@@ -26291,7 +26232,7 @@
       <c r="Z328" s="1"/>
       <c r="AA328" s="1"/>
     </row>
-    <row r="329" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="8" t="s">
         <v>234</v>
       </c>
@@ -26358,7 +26299,7 @@
       <c r="Z329" s="1"/>
       <c r="AA329" s="1"/>
     </row>
-    <row r="330" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="8" t="s">
         <v>482</v>
       </c>
@@ -26425,7 +26366,7 @@
       <c r="Z330" s="1"/>
       <c r="AA330" s="1"/>
     </row>
-    <row r="331" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="8" t="s">
         <v>240</v>
       </c>
@@ -26492,7 +26433,7 @@
       <c r="Z331" s="1"/>
       <c r="AA331" s="1"/>
     </row>
-    <row r="332" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="8" t="s">
         <v>456</v>
       </c>
@@ -26559,7 +26500,7 @@
       <c r="Z332" s="1"/>
       <c r="AA332" s="1"/>
     </row>
-    <row r="333" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="8" t="s">
         <v>160</v>
       </c>
@@ -26626,7 +26567,7 @@
       <c r="Z333" s="1"/>
       <c r="AA333" s="1"/>
     </row>
-    <row r="334" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="8" t="s">
         <v>462</v>
       </c>
@@ -26693,7 +26634,7 @@
       <c r="Z334" s="1"/>
       <c r="AA334" s="1"/>
     </row>
-    <row r="335" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="8" t="s">
         <v>130</v>
       </c>
@@ -26760,7 +26701,7 @@
       <c r="Z335" s="1"/>
       <c r="AA335" s="1"/>
     </row>
-    <row r="336" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="8" t="s">
         <v>518</v>
       </c>
@@ -26827,7 +26768,7 @@
       <c r="Z336" s="1"/>
       <c r="AA336" s="1"/>
     </row>
-    <row r="337" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="8" t="s">
         <v>46</v>
       </c>
@@ -26894,7 +26835,7 @@
       <c r="Z337" s="1"/>
       <c r="AA337" s="1"/>
     </row>
-    <row r="338" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="8" t="s">
         <v>330</v>
       </c>
@@ -26961,7 +26902,7 @@
       <c r="Z338" s="1"/>
       <c r="AA338" s="1"/>
     </row>
-    <row r="339" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="8" t="s">
         <v>222</v>
       </c>
@@ -27028,7 +26969,7 @@
       <c r="Z339" s="1"/>
       <c r="AA339" s="1"/>
     </row>
-    <row r="340" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="8" t="s">
         <v>394</v>
       </c>
@@ -27095,7 +27036,7 @@
       <c r="Z340" s="1"/>
       <c r="AA340" s="1"/>
     </row>
-    <row r="341" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="8" t="s">
         <v>190</v>
       </c>
@@ -27162,7 +27103,7 @@
       <c r="Z341" s="1"/>
       <c r="AA341" s="1"/>
     </row>
-    <row r="342" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="8" t="s">
         <v>308</v>
       </c>
@@ -27229,7 +27170,7 @@
       <c r="Z342" s="1"/>
       <c r="AA342" s="1"/>
     </row>
-    <row r="343" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="8" t="s">
         <v>376</v>
       </c>
@@ -27296,7 +27237,7 @@
       <c r="Z343" s="1"/>
       <c r="AA343" s="1"/>
     </row>
-    <row r="344" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="8" t="s">
         <v>37</v>
       </c>
@@ -27363,7 +27304,7 @@
       <c r="Z344" s="1"/>
       <c r="AA344" s="1"/>
     </row>
-    <row r="345" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="8" t="s">
         <v>306</v>
       </c>
@@ -27430,7 +27371,7 @@
       <c r="Z345" s="1"/>
       <c r="AA345" s="1"/>
     </row>
-    <row r="346" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="8" t="s">
         <v>438</v>
       </c>
@@ -27497,7 +27438,7 @@
       <c r="Z346" s="1"/>
       <c r="AA346" s="1"/>
     </row>
-    <row r="347" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="8" t="s">
         <v>388</v>
       </c>
@@ -27564,7 +27505,7 @@
       <c r="Z347" s="1"/>
       <c r="AA347" s="1"/>
     </row>
-    <row r="348" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="8" t="s">
         <v>538</v>
       </c>
@@ -27631,7 +27572,7 @@
       <c r="Z348" s="1"/>
       <c r="AA348" s="1"/>
     </row>
-    <row r="349" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="8" t="s">
         <v>32</v>
       </c>
@@ -27698,7 +27639,7 @@
       <c r="Z349" s="1"/>
       <c r="AA349" s="1"/>
     </row>
-    <row r="350" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="8" t="s">
         <v>310</v>
       </c>
@@ -27765,7 +27706,7 @@
       <c r="Z350" s="1"/>
       <c r="AA350" s="1"/>
     </row>
-    <row r="351" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="8" t="s">
         <v>470</v>
       </c>
@@ -27832,7 +27773,7 @@
       <c r="Z351" s="1"/>
       <c r="AA351" s="1"/>
     </row>
-    <row r="352" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="8" t="s">
         <v>174</v>
       </c>
@@ -27899,7 +27840,7 @@
       <c r="Z352" s="1"/>
       <c r="AA352" s="1"/>
     </row>
-    <row r="353" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="8" t="s">
         <v>540</v>
       </c>
@@ -27966,7 +27907,7 @@
       <c r="Z353" s="1"/>
       <c r="AA353" s="1"/>
     </row>
-    <row r="354" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="8" t="s">
         <v>136</v>
       </c>
@@ -28033,7 +27974,7 @@
       <c r="Z354" s="1"/>
       <c r="AA354" s="1"/>
     </row>
-    <row r="355" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="8" t="s">
         <v>532</v>
       </c>
@@ -28100,7 +28041,7 @@
       <c r="Z355" s="1"/>
       <c r="AA355" s="1"/>
     </row>
-    <row r="356" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="8" t="s">
         <v>196</v>
       </c>
@@ -28167,7 +28108,7 @@
       <c r="Z356" s="1"/>
       <c r="AA356" s="1"/>
     </row>
-    <row r="357" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="8" t="s">
         <v>214</v>
       </c>
@@ -28234,7 +28175,7 @@
       <c r="Z357" s="1"/>
       <c r="AA357" s="1"/>
     </row>
-    <row r="358" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="8" t="s">
         <v>444</v>
       </c>
@@ -28301,7 +28242,7 @@
       <c r="Z358" s="1"/>
       <c r="AA358" s="1"/>
     </row>
-    <row r="359" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="8" t="s">
         <v>228</v>
       </c>
@@ -28368,7 +28309,7 @@
       <c r="Z359" s="1"/>
       <c r="AA359" s="1"/>
     </row>
-    <row r="360" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="8" t="s">
         <v>436</v>
       </c>
@@ -28435,7 +28376,7 @@
       <c r="Z360" s="1"/>
       <c r="AA360" s="1"/>
     </row>
-    <row r="361" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="8" t="s">
         <v>172</v>
       </c>
@@ -28502,7 +28443,7 @@
       <c r="Z361" s="1"/>
       <c r="AA361" s="1"/>
     </row>
-    <row r="362" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="8" t="s">
         <v>420</v>
       </c>
@@ -28569,7 +28510,7 @@
       <c r="Z362" s="1"/>
       <c r="AA362" s="1"/>
     </row>
-    <row r="363" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="8" t="s">
         <v>69</v>
       </c>
@@ -28636,7 +28577,7 @@
       <c r="Z363" s="1"/>
       <c r="AA363" s="1"/>
     </row>
-    <row r="364" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="8" t="s">
         <v>152</v>
       </c>
@@ -28703,7 +28644,7 @@
       <c r="Z364" s="1"/>
       <c r="AA364" s="1"/>
     </row>
-    <row r="365" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="8" t="s">
         <v>77</v>
       </c>
@@ -28770,7 +28711,7 @@
       <c r="Z365" s="1"/>
       <c r="AA365" s="1"/>
     </row>
-    <row r="366" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="8" t="s">
         <v>506</v>
       </c>
@@ -28837,7 +28778,7 @@
       <c r="Z366" s="1"/>
       <c r="AA366" s="1"/>
     </row>
-    <row r="367" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="8" t="s">
         <v>320</v>
       </c>
@@ -28904,7 +28845,7 @@
       <c r="Z367" s="1"/>
       <c r="AA367" s="1"/>
     </row>
-    <row r="368" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="8" t="s">
         <v>86</v>
       </c>
@@ -28971,7 +28912,7 @@
       <c r="Z368" s="1"/>
       <c r="AA368" s="1"/>
     </row>
-    <row r="369" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="8" t="s">
         <v>252</v>
       </c>
@@ -29038,7 +28979,7 @@
       <c r="Z369" s="1"/>
       <c r="AA369" s="1"/>
     </row>
-    <row r="370" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="8" t="s">
         <v>380</v>
       </c>
@@ -29105,7 +29046,7 @@
       <c r="Z370" s="1"/>
       <c r="AA370" s="1"/>
     </row>
-    <row r="371" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="8" t="s">
         <v>142</v>
       </c>
@@ -29172,7 +29113,7 @@
       <c r="Z371" s="1"/>
       <c r="AA371" s="1"/>
     </row>
-    <row r="372" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="8" t="s">
         <v>114</v>
       </c>
@@ -29239,7 +29180,7 @@
       <c r="Z372" s="1"/>
       <c r="AA372" s="1"/>
     </row>
-    <row r="373" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="8" t="s">
         <v>300</v>
       </c>
@@ -29306,7 +29247,7 @@
       <c r="Z373" s="1"/>
       <c r="AA373" s="1"/>
     </row>
-    <row r="374" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="8" t="s">
         <v>262</v>
       </c>
@@ -29373,7 +29314,7 @@
       <c r="Z374" s="1"/>
       <c r="AA374" s="1"/>
     </row>
-    <row r="375" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="8" t="s">
         <v>270</v>
       </c>
@@ -29440,7 +29381,7 @@
       <c r="Z375" s="1"/>
       <c r="AA375" s="1"/>
     </row>
-    <row r="376" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="8" t="s">
         <v>324</v>
       </c>
@@ -29507,7 +29448,7 @@
       <c r="Z376" s="1"/>
       <c r="AA376" s="1"/>
     </row>
-    <row r="377" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="8" t="s">
         <v>122</v>
       </c>
@@ -29574,7 +29515,7 @@
       <c r="Z377" s="1"/>
       <c r="AA377" s="1"/>
     </row>
-    <row r="378" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="8" t="s">
         <v>294</v>
       </c>
@@ -29641,7 +29582,7 @@
       <c r="Z378" s="1"/>
       <c r="AA378" s="1"/>
     </row>
-    <row r="379" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="8" t="s">
         <v>426</v>
       </c>
@@ -29708,7 +29649,7 @@
       <c r="Z379" s="1"/>
       <c r="AA379" s="1"/>
     </row>
-    <row r="380" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="8" t="s">
         <v>302</v>
       </c>
@@ -29775,7 +29716,7 @@
       <c r="Z380" s="1"/>
       <c r="AA380" s="1"/>
     </row>
-    <row r="381" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="8" t="s">
         <v>280</v>
       </c>
@@ -29842,7 +29783,7 @@
       <c r="Z381" s="1"/>
       <c r="AA381" s="1"/>
     </row>
-    <row r="382" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="8" t="s">
         <v>166</v>
       </c>
@@ -29909,7 +29850,7 @@
       <c r="Z382" s="1"/>
       <c r="AA382" s="1"/>
     </row>
-    <row r="383" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="8" t="s">
         <v>97</v>
       </c>
@@ -29976,7 +29917,7 @@
       <c r="Z383" s="1"/>
       <c r="AA383" s="1"/>
     </row>
-    <row r="384" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="8" t="s">
         <v>268</v>
       </c>
@@ -30043,7 +29984,7 @@
       <c r="Z384" s="1"/>
       <c r="AA384" s="1"/>
     </row>
-    <row r="385" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="8" t="s">
         <v>458</v>
       </c>
@@ -30110,7 +30051,7 @@
       <c r="Z385" s="1"/>
       <c r="AA385" s="1"/>
     </row>
-    <row r="386" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="8" t="s">
         <v>446</v>
       </c>
@@ -30177,7 +30118,7 @@
       <c r="Z386" s="1"/>
       <c r="AA386" s="1"/>
     </row>
-    <row r="387" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="8" t="s">
         <v>322</v>
       </c>
@@ -30244,7 +30185,7 @@
       <c r="Z387" s="1"/>
       <c r="AA387" s="1"/>
     </row>
-    <row r="388" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="8" t="s">
         <v>452</v>
       </c>
@@ -30311,7 +30252,7 @@
       <c r="Z388" s="1"/>
       <c r="AA388" s="1"/>
     </row>
-    <row r="389" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="8" t="s">
         <v>63</v>
       </c>
@@ -30378,7 +30319,7 @@
       <c r="Z389" s="1"/>
       <c r="AA389" s="1"/>
     </row>
-    <row r="390" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="8" t="s">
         <v>224</v>
       </c>
@@ -30445,7 +30386,7 @@
       <c r="Z390" s="1"/>
       <c r="AA390" s="1"/>
     </row>
-    <row r="391" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="8" t="s">
         <v>134</v>
       </c>
@@ -30512,7 +30453,7 @@
       <c r="Z391" s="1"/>
       <c r="AA391" s="1"/>
     </row>
-    <row r="392" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="8" t="s">
         <v>460</v>
       </c>
@@ -30579,7 +30520,7 @@
       <c r="Z392" s="1"/>
       <c r="AA392" s="1"/>
     </row>
-    <row r="393" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="8" t="s">
         <v>374</v>
       </c>
@@ -30646,7 +30587,7 @@
       <c r="Z393" s="1"/>
       <c r="AA393" s="1"/>
     </row>
-    <row r="394" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="8" t="s">
         <v>368</v>
       </c>
@@ -30713,7 +30654,7 @@
       <c r="Z394" s="1"/>
       <c r="AA394" s="1"/>
     </row>
-    <row r="395" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="8" t="s">
         <v>500</v>
       </c>
@@ -30780,7 +30721,7 @@
       <c r="Z395" s="1"/>
       <c r="AA395" s="1"/>
     </row>
-    <row r="396" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="8" t="s">
         <v>242</v>
       </c>
@@ -30847,7 +30788,7 @@
       <c r="Z396" s="1"/>
       <c r="AA396" s="1"/>
     </row>
-    <row r="397" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="8" t="s">
         <v>204</v>
       </c>
@@ -30914,7 +30855,7 @@
       <c r="Z397" s="1"/>
       <c r="AA397" s="1"/>
     </row>
-    <row r="398" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="8" t="s">
         <v>298</v>
       </c>
@@ -30981,7 +30922,7 @@
       <c r="Z398" s="1"/>
       <c r="AA398" s="1"/>
     </row>
-    <row r="399" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="8" t="s">
         <v>266</v>
       </c>
@@ -31048,7 +30989,7 @@
       <c r="Z399" s="1"/>
       <c r="AA399" s="1"/>
     </row>
-    <row r="400" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="8" t="s">
         <v>428</v>
       </c>
@@ -31115,7 +31056,7 @@
       <c r="Z400" s="1"/>
       <c r="AA400" s="1"/>
     </row>
-    <row r="401" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="8" t="s">
         <v>464</v>
       </c>
@@ -31182,7 +31123,7 @@
       <c r="Z401" s="1"/>
       <c r="AA401" s="1"/>
     </row>
-    <row r="402" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="8" t="s">
         <v>246</v>
       </c>
@@ -31249,7 +31190,7 @@
       <c r="Z402" s="1"/>
       <c r="AA402" s="1"/>
     </row>
-    <row r="403" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="8" t="s">
         <v>404</v>
       </c>
@@ -31316,7 +31257,7 @@
       <c r="Z403" s="1"/>
       <c r="AA403" s="1"/>
     </row>
-    <row r="404" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="8" t="s">
         <v>170</v>
       </c>
@@ -31383,7 +31324,7 @@
       <c r="Z404" s="1"/>
       <c r="AA404" s="1"/>
     </row>
-    <row r="405" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="8" t="s">
         <v>508</v>
       </c>
@@ -31450,7 +31391,7 @@
       <c r="Z405" s="1"/>
       <c r="AA405" s="1"/>
     </row>
-    <row r="406" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="8" t="s">
         <v>212</v>
       </c>
@@ -31517,7 +31458,7 @@
       <c r="Z406" s="1"/>
       <c r="AA406" s="1"/>
     </row>
-    <row r="407" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="8" t="s">
         <v>430</v>
       </c>
@@ -31584,7 +31525,7 @@
       <c r="Z407" s="1"/>
       <c r="AA407" s="1"/>
     </row>
-    <row r="408" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="8" t="s">
         <v>370</v>
       </c>
@@ -31651,7 +31592,7 @@
       <c r="Z408" s="1"/>
       <c r="AA408" s="1"/>
     </row>
-    <row r="409" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="8" t="s">
         <v>384</v>
       </c>
@@ -31718,7 +31659,7 @@
       <c r="Z409" s="1"/>
       <c r="AA409" s="1"/>
     </row>
-    <row r="410" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="8" t="s">
         <v>466</v>
       </c>
@@ -31785,7 +31726,7 @@
       <c r="Z410" s="1"/>
       <c r="AA410" s="1"/>
     </row>
-    <row r="411" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="8" t="s">
         <v>188</v>
       </c>
@@ -31852,7 +31793,7 @@
       <c r="Z411" s="1"/>
       <c r="AA411" s="1"/>
     </row>
-    <row r="412" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="8" t="s">
         <v>536</v>
       </c>
@@ -31919,7 +31860,7 @@
       <c r="Z412" s="1"/>
       <c r="AA412" s="1"/>
     </row>
-    <row r="413" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="8" t="s">
         <v>318</v>
       </c>
@@ -31986,7 +31927,7 @@
       <c r="Z413" s="1"/>
       <c r="AA413" s="1"/>
     </row>
-    <row r="414" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="8" t="s">
         <v>138</v>
       </c>
@@ -32053,7 +31994,7 @@
       <c r="Z414" s="1"/>
       <c r="AA414" s="1"/>
     </row>
-    <row r="415" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="8" t="s">
         <v>162</v>
       </c>
@@ -32120,7 +32061,7 @@
       <c r="Z415" s="1"/>
       <c r="AA415" s="1"/>
     </row>
-    <row r="416" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="8" t="s">
         <v>92</v>
       </c>
@@ -32187,7 +32128,7 @@
       <c r="Z416" s="1"/>
       <c r="AA416" s="1"/>
     </row>
-    <row r="417" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="8" t="s">
         <v>202</v>
       </c>
@@ -32254,7 +32195,7 @@
       <c r="Z417" s="1"/>
       <c r="AA417" s="1"/>
     </row>
-    <row r="418" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="8" t="s">
         <v>112</v>
       </c>
@@ -32321,7 +32262,7 @@
       <c r="Z418" s="1"/>
       <c r="AA418" s="1"/>
     </row>
-    <row r="419" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="8" t="s">
         <v>520</v>
       </c>
@@ -32388,7 +32329,7 @@
       <c r="Z419" s="1"/>
       <c r="AA419" s="1"/>
     </row>
-    <row r="420" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="8" t="s">
         <v>210</v>
       </c>
@@ -32455,7 +32396,7 @@
       <c r="Z420" s="1"/>
       <c r="AA420" s="1"/>
     </row>
-    <row r="421" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="8" t="s">
         <v>200</v>
       </c>
@@ -32522,7 +32463,7 @@
       <c r="Z421" s="1"/>
       <c r="AA421" s="1"/>
     </row>
-    <row r="422" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="8" t="s">
         <v>256</v>
       </c>
@@ -32589,7 +32530,7 @@
       <c r="Z422" s="1"/>
       <c r="AA422" s="1"/>
     </row>
-    <row r="423" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="8" t="s">
         <v>218</v>
       </c>
@@ -32656,7 +32597,7 @@
       <c r="Z423" s="1"/>
       <c r="AA423" s="1"/>
     </row>
-    <row r="424" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="8" t="s">
         <v>434</v>
       </c>
@@ -32723,7 +32664,7 @@
       <c r="Z424" s="1"/>
       <c r="AA424" s="1"/>
     </row>
-    <row r="425" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="8" t="s">
         <v>348</v>
       </c>
@@ -32790,7 +32731,7 @@
       <c r="Z425" s="1"/>
       <c r="AA425" s="1"/>
     </row>
-    <row r="426" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="8" t="s">
         <v>184</v>
       </c>
@@ -32857,7 +32798,7 @@
       <c r="Z426" s="1"/>
       <c r="AA426" s="1"/>
     </row>
-    <row r="427" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="8" t="s">
         <v>148</v>
       </c>
@@ -32924,7 +32865,7 @@
       <c r="Z427" s="1"/>
       <c r="AA427" s="1"/>
     </row>
-    <row r="428" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="8" t="s">
         <v>362</v>
       </c>
@@ -32991,7 +32932,7 @@
       <c r="Z428" s="1"/>
       <c r="AA428" s="1"/>
     </row>
-    <row r="429" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="8" t="s">
         <v>88</v>
       </c>
@@ -33058,7 +32999,7 @@
       <c r="Z429" s="1"/>
       <c r="AA429" s="1"/>
     </row>
-    <row r="430" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="8" t="s">
         <v>288</v>
       </c>
@@ -33125,7 +33066,7 @@
       <c r="Z430" s="1"/>
       <c r="AA430" s="1"/>
     </row>
-    <row r="431" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="8" t="s">
         <v>448</v>
       </c>
@@ -33192,7 +33133,7 @@
       <c r="Z431" s="1"/>
       <c r="AA431" s="1"/>
     </row>
-    <row r="432" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="8" t="s">
         <v>314</v>
       </c>
@@ -33259,7 +33200,7 @@
       <c r="Z432" s="1"/>
       <c r="AA432" s="1"/>
     </row>
-    <row r="433" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="8" t="s">
         <v>264</v>
       </c>
@@ -33326,7 +33267,7 @@
       <c r="Z433" s="1"/>
       <c r="AA433" s="1"/>
     </row>
-    <row r="434" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="8" t="s">
         <v>396</v>
       </c>
@@ -33393,7 +33334,7 @@
       <c r="Z434" s="1"/>
       <c r="AA434" s="1"/>
     </row>
-    <row r="435" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="8" t="s">
         <v>516</v>
       </c>
@@ -33460,7 +33401,7 @@
       <c r="Z435" s="1"/>
       <c r="AA435" s="1"/>
     </row>
-    <row r="436" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="8" t="s">
         <v>58</v>
       </c>
@@ -33527,7 +33468,7 @@
       <c r="Z436" s="1"/>
       <c r="AA436" s="1"/>
     </row>
-    <row r="437" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="8" t="s">
         <v>474</v>
       </c>
@@ -33594,7 +33535,7 @@
       <c r="Z437" s="1"/>
       <c r="AA437" s="1"/>
     </row>
-    <row r="438" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="8" t="s">
         <v>418</v>
       </c>
@@ -33661,7 +33602,7 @@
       <c r="Z438" s="1"/>
       <c r="AA438" s="1"/>
     </row>
-    <row r="439" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="8" t="s">
         <v>484</v>
       </c>
@@ -33728,7 +33669,7 @@
       <c r="Z439" s="1"/>
       <c r="AA439" s="1"/>
     </row>
-    <row r="440" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="8" t="s">
         <v>304</v>
       </c>
@@ -33795,7 +33736,7 @@
       <c r="Z440" s="1"/>
       <c r="AA440" s="1"/>
     </row>
-    <row r="441" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="8" t="s">
         <v>342</v>
       </c>
@@ -33862,7 +33803,7 @@
       <c r="Z441" s="1"/>
       <c r="AA441" s="1"/>
     </row>
-    <row r="442" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="8" t="s">
         <v>386</v>
       </c>
@@ -33929,7 +33870,7 @@
       <c r="Z442" s="1"/>
       <c r="AA442" s="1"/>
     </row>
-    <row r="443" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="8" t="s">
         <v>478</v>
       </c>
@@ -33996,7 +33937,7 @@
       <c r="Z443" s="1"/>
       <c r="AA443" s="1"/>
     </row>
-    <row r="444" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="8" t="s">
         <v>82</v>
       </c>
@@ -34063,7 +34004,7 @@
       <c r="Z444" s="1"/>
       <c r="AA444" s="1"/>
     </row>
-    <row r="445" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="8" t="s">
         <v>332</v>
       </c>
@@ -34130,7 +34071,7 @@
       <c r="Z445" s="1"/>
       <c r="AA445" s="1"/>
     </row>
-    <row r="446" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="8" t="s">
         <v>66</v>
       </c>
@@ -34197,7 +34138,7 @@
       <c r="Z446" s="1"/>
       <c r="AA446" s="1"/>
     </row>
-    <row r="447" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="8" t="s">
         <v>168</v>
       </c>
@@ -34264,7 +34205,7 @@
       <c r="Z447" s="1"/>
       <c r="AA447" s="1"/>
     </row>
-    <row r="448" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="8" t="s">
         <v>73</v>
       </c>
@@ -34331,7 +34272,7 @@
       <c r="Z448" s="1"/>
       <c r="AA448" s="1"/>
     </row>
-    <row r="449" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="8" t="s">
         <v>422</v>
       </c>
@@ -34398,7 +34339,7 @@
       <c r="Z449" s="1"/>
       <c r="AA449" s="1"/>
     </row>
-    <row r="450" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="8" t="s">
         <v>400</v>
       </c>
@@ -34465,7 +34406,7 @@
       <c r="Z450" s="1"/>
       <c r="AA450" s="1"/>
     </row>
-    <row r="451" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="8" t="s">
         <v>52</v>
       </c>
@@ -34532,7 +34473,7 @@
       <c r="Z451" s="1"/>
       <c r="AA451" s="1"/>
     </row>
-    <row r="452" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="8" t="s">
         <v>524</v>
       </c>
@@ -34599,7 +34540,7 @@
       <c r="Z452" s="1"/>
       <c r="AA452" s="1"/>
     </row>
-    <row r="453" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="8" t="s">
         <v>326</v>
       </c>
@@ -34666,7 +34607,7 @@
       <c r="Z453" s="1"/>
       <c r="AA453" s="1"/>
     </row>
-    <row r="454" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="8" t="s">
         <v>17</v>
       </c>
@@ -34733,7 +34674,7 @@
       <c r="Z454" s="1"/>
       <c r="AA454" s="1"/>
     </row>
-    <row r="455" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="8" t="s">
         <v>180</v>
       </c>
@@ -34800,7 +34741,7 @@
       <c r="Z455" s="1"/>
       <c r="AA455" s="1"/>
     </row>
-    <row r="456" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="8" t="s">
         <v>410</v>
       </c>
@@ -34867,7 +34808,7 @@
       <c r="Z456" s="1"/>
       <c r="AA456" s="1"/>
     </row>
-    <row r="457" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="8" t="s">
         <v>116</v>
       </c>
@@ -34934,7 +34875,7 @@
       <c r="Z457" s="1"/>
       <c r="AA457" s="1"/>
     </row>
-    <row r="458" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="8" t="s">
         <v>408</v>
       </c>
@@ -35001,7 +34942,7 @@
       <c r="Z458" s="1"/>
       <c r="AA458" s="1"/>
     </row>
-    <row r="459" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="8" t="s">
         <v>206</v>
       </c>
@@ -35068,7 +35009,7 @@
       <c r="Z459" s="1"/>
       <c r="AA459" s="1"/>
     </row>
-    <row r="460" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="8" t="s">
         <v>372</v>
       </c>
@@ -35135,7 +35076,7 @@
       <c r="Z460" s="1"/>
       <c r="AA460" s="1"/>
     </row>
-    <row r="461" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="8" t="s">
         <v>110</v>
       </c>
@@ -35202,7 +35143,7 @@
       <c r="Z461" s="1"/>
       <c r="AA461" s="1"/>
     </row>
-    <row r="462" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="8" t="s">
         <v>504</v>
       </c>
@@ -35269,7 +35210,7 @@
       <c r="Z462" s="1"/>
       <c r="AA462" s="1"/>
     </row>
-    <row r="463" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="8" t="s">
         <v>490</v>
       </c>
@@ -35336,7 +35277,7 @@
       <c r="Z463" s="1"/>
       <c r="AA463" s="1"/>
     </row>
-    <row r="464" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="8" t="s">
         <v>424</v>
       </c>
@@ -35403,7 +35344,7 @@
       <c r="Z464" s="1"/>
       <c r="AA464" s="1"/>
     </row>
-    <row r="465" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="8" t="s">
         <v>488</v>
       </c>
@@ -35470,7 +35411,7 @@
       <c r="Z465" s="1"/>
       <c r="AA465" s="1"/>
     </row>
-    <row r="466" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="8" t="s">
         <v>90</v>
       </c>
@@ -35537,7 +35478,7 @@
       <c r="Z466" s="1"/>
       <c r="AA466" s="1"/>
     </row>
-    <row r="467" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="8" t="s">
         <v>292</v>
       </c>
@@ -35604,7 +35545,7 @@
       <c r="Z467" s="1"/>
       <c r="AA467" s="1"/>
     </row>
-    <row r="468" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="8" t="s">
         <v>346</v>
       </c>
@@ -35671,7 +35612,7 @@
       <c r="Z468" s="1"/>
       <c r="AA468" s="1"/>
     </row>
-    <row r="469" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="8" t="s">
         <v>312</v>
       </c>
@@ -35738,7 +35679,7 @@
       <c r="Z469" s="1"/>
       <c r="AA469" s="1"/>
     </row>
-    <row r="470" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="8" t="s">
         <v>118</v>
       </c>
@@ -35805,7 +35746,7 @@
       <c r="Z470" s="1"/>
       <c r="AA470" s="1"/>
     </row>
-    <row r="471" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="8" t="s">
         <v>198</v>
       </c>
@@ -35872,7 +35813,7 @@
       <c r="Z471" s="1"/>
       <c r="AA471" s="1"/>
     </row>
-    <row r="472" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="8" t="s">
         <v>360</v>
       </c>
@@ -35939,7 +35880,7 @@
       <c r="Z472" s="1"/>
       <c r="AA472" s="1"/>
     </row>
-    <row r="473" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="8" t="s">
         <v>140</v>
       </c>
@@ -36006,7 +35947,7 @@
       <c r="Z473" s="1"/>
       <c r="AA473" s="1"/>
     </row>
-    <row r="474" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="8" t="s">
         <v>486</v>
       </c>
@@ -36073,7 +36014,7 @@
       <c r="Z474" s="1"/>
       <c r="AA474" s="1"/>
     </row>
-    <row r="475" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="8" t="s">
         <v>480</v>
       </c>
@@ -36140,7 +36081,7 @@
       <c r="Z475" s="1"/>
       <c r="AA475" s="1"/>
     </row>
-    <row r="476" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="8" t="s">
         <v>44</v>
       </c>
@@ -36207,7 +36148,7 @@
       <c r="Z476" s="1"/>
       <c r="AA476" s="1"/>
     </row>
-    <row r="477" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="8" t="s">
         <v>194</v>
       </c>
@@ -36274,7 +36215,7 @@
       <c r="Z477" s="1"/>
       <c r="AA477" s="1"/>
     </row>
-    <row r="478" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="8" t="s">
         <v>108</v>
       </c>
@@ -36341,7 +36282,7 @@
       <c r="Z478" s="1"/>
       <c r="AA478" s="1"/>
     </row>
-    <row r="479" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="8" t="s">
         <v>274</v>
       </c>
@@ -36408,7 +36349,7 @@
       <c r="Z479" s="1"/>
       <c r="AA479" s="1"/>
     </row>
-    <row r="480" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="8" t="s">
         <v>498</v>
       </c>
@@ -36475,7 +36416,7 @@
       <c r="Z480" s="1"/>
       <c r="AA480" s="1"/>
     </row>
-    <row r="481" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="8" t="s">
         <v>472</v>
       </c>
@@ -36542,7 +36483,7 @@
       <c r="Z481" s="1"/>
       <c r="AA481" s="1"/>
     </row>
-    <row r="482" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="8" t="s">
         <v>468</v>
       </c>
@@ -36609,7 +36550,7 @@
       <c r="Z482" s="1"/>
       <c r="AA482" s="1"/>
     </row>
-    <row r="483" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="8" t="s">
         <v>340</v>
       </c>
@@ -36676,7 +36617,7 @@
       <c r="Z483" s="1"/>
       <c r="AA483" s="1"/>
     </row>
-    <row r="484" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="8" t="s">
         <v>192</v>
       </c>
@@ -36743,7 +36684,7 @@
       <c r="Z484" s="1"/>
       <c r="AA484" s="1"/>
     </row>
-    <row r="485" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="8" t="s">
         <v>158</v>
       </c>
@@ -36810,7 +36751,7 @@
       <c r="Z485" s="1"/>
       <c r="AA485" s="1"/>
     </row>
-    <row r="486" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="8" t="s">
         <v>144</v>
       </c>
@@ -36877,7 +36818,7 @@
       <c r="Z486" s="1"/>
       <c r="AA486" s="1"/>
     </row>
-    <row r="487" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="8" t="s">
         <v>60</v>
       </c>
@@ -36944,7 +36885,7 @@
       <c r="Z487" s="1"/>
       <c r="AA487" s="1"/>
     </row>
-    <row r="488" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="8" t="s">
         <v>350</v>
       </c>
@@ -37011,7 +36952,7 @@
       <c r="Z488" s="1"/>
       <c r="AA488" s="1"/>
     </row>
-    <row r="489" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="8" t="s">
         <v>272</v>
       </c>
@@ -37078,7 +37019,7 @@
       <c r="Z489" s="1"/>
       <c r="AA489" s="1"/>
     </row>
-    <row r="490" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="8" t="s">
         <v>248</v>
       </c>
@@ -37145,7 +37086,7 @@
       <c r="Z490" s="1"/>
       <c r="AA490" s="1"/>
     </row>
-    <row r="491" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="8" t="s">
         <v>100</v>
       </c>
@@ -37212,7 +37153,7 @@
       <c r="Z491" s="1"/>
       <c r="AA491" s="1"/>
     </row>
-    <row r="492" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="8" t="s">
         <v>390</v>
       </c>
@@ -37279,7 +37220,7 @@
       <c r="Z492" s="1"/>
       <c r="AA492" s="1"/>
     </row>
-    <row r="493" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="8" t="s">
         <v>128</v>
       </c>
@@ -37346,7 +37287,7 @@
       <c r="Z493" s="1"/>
       <c r="AA493" s="1"/>
     </row>
-    <row r="494" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="8" t="s">
         <v>71</v>
       </c>
@@ -37413,7 +37354,7 @@
       <c r="Z494" s="1"/>
       <c r="AA494" s="1"/>
     </row>
-    <row r="495" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="8" t="s">
         <v>510</v>
       </c>
@@ -37480,7 +37421,7 @@
       <c r="Z495" s="1"/>
       <c r="AA495" s="1"/>
     </row>
-    <row r="496" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="8" t="s">
         <v>412</v>
       </c>
@@ -37547,7 +37488,7 @@
       <c r="Z496" s="1"/>
       <c r="AA496" s="1"/>
     </row>
-    <row r="497" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="8" t="s">
         <v>528</v>
       </c>
@@ -37614,7 +37555,7 @@
       <c r="Z497" s="1"/>
       <c r="AA497" s="1"/>
     </row>
-    <row r="498" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="8" t="s">
         <v>146</v>
       </c>
@@ -37681,7 +37622,7 @@
       <c r="Z498" s="1"/>
       <c r="AA498" s="1"/>
     </row>
-    <row r="499" spans="1:27" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="8" t="s">
         <v>182</v>
       </c>
@@ -37749,29 +37690,29 @@
       <c r="AA499" s="1"/>
     </row>
     <row r="500" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A500" s="80"/>
-      <c r="B500" s="81"/>
-      <c r="C500" s="81"/>
-      <c r="D500" s="82" t="s">
+      <c r="A500" s="77"/>
+      <c r="B500" s="78"/>
+      <c r="C500" s="78"/>
+      <c r="D500" s="79" t="s">
         <v>684</v>
       </c>
-      <c r="E500" s="82">
+      <c r="E500" s="79">
         <f>SUBTOTAL(109,Table3[sales])</f>
-        <v>334964.15999999997</v>
-      </c>
-      <c r="F500" s="82"/>
-      <c r="G500" s="83"/>
-      <c r="H500" s="82"/>
-      <c r="I500" s="84"/>
-      <c r="J500" s="84"/>
-      <c r="K500" s="84"/>
-      <c r="L500" s="82"/>
-      <c r="M500" s="82"/>
-      <c r="N500" s="82"/>
-      <c r="O500" s="82"/>
-      <c r="P500" s="85"/>
-      <c r="Q500" s="86"/>
-      <c r="R500" s="82"/>
+        <v>1322669.1900000006</v>
+      </c>
+      <c r="F500" s="79"/>
+      <c r="G500" s="80"/>
+      <c r="H500" s="79"/>
+      <c r="I500" s="81"/>
+      <c r="J500" s="81"/>
+      <c r="K500" s="81"/>
+      <c r="L500" s="79"/>
+      <c r="M500" s="79"/>
+      <c r="N500" s="79"/>
+      <c r="O500" s="79"/>
+      <c r="P500" s="82"/>
+      <c r="Q500" s="83"/>
+      <c r="R500" s="79"/>
       <c r="S500" s="1"/>
       <c r="T500" s="1"/>
       <c r="U500" s="1"/>
@@ -37787,7 +37728,7 @@
       </c>
       <c r="E501" s="1">
         <f>SUBTOTAL(9,Table3[sales])</f>
-        <v>334964.15999999997</v>
+        <v>1322669.1900000006</v>
       </c>
       <c r="F501" s="1"/>
       <c r="G501" s="33"/>
@@ -50299,15 +50240,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50969,10 +50910,10 @@
   </sortState>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B1:B9">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>20000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
       <formula>50000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51584,7 +51525,7 @@
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="76" t="s">
         <v>681</v>
       </c>
       <c r="C22">
@@ -51593,7 +51534,7 @@
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="76" t="s">
         <v>682</v>
       </c>
       <c r="C23">
@@ -51602,7 +51543,7 @@
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" s="78" t="s">
+      <c r="B24" s="76" t="s">
         <v>683</v>
       </c>
       <c r="C24">
@@ -51611,7 +51552,7 @@
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="76" t="s">
         <v>682</v>
       </c>
       <c r="C25">
@@ -51623,4 +51564,226 @@
   <autoFilter ref="C15:C24" xr:uid="{F24C003C-206A-4005-AB81-1F886CB6485B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FCD3B0-4BC8-4681-8037-4E058512B5F9}">
+  <dimension ref="B1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="85" t="s">
+        <v>686</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>600</v>
+      </c>
+      <c r="D2" s="85" t="s">
+        <v>577</v>
+      </c>
+      <c r="E2" s="85" t="s">
+        <v>624</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="25">
+        <v>1001</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>604</v>
+      </c>
+      <c r="D3" s="25">
+        <v>70000</v>
+      </c>
+      <c r="E3" s="84">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="25">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="25">
+        <v>1002</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>605</v>
+      </c>
+      <c r="D4" s="25">
+        <v>50000</v>
+      </c>
+      <c r="E4" s="84">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="25">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="25">
+        <v>1003</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>606</v>
+      </c>
+      <c r="D5" s="25">
+        <v>45000</v>
+      </c>
+      <c r="E5" s="84">
+        <v>0</v>
+      </c>
+      <c r="F5" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="25">
+        <v>1004</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="D6" s="25">
+        <v>75000</v>
+      </c>
+      <c r="E6" s="84">
+        <v>0.15</v>
+      </c>
+      <c r="F6" s="25">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="25">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>623</v>
+      </c>
+      <c r="D7" s="25">
+        <v>55000</v>
+      </c>
+      <c r="E7" s="84">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="25">
+        <v>2750</v>
+      </c>
+      <c r="G7" t="s">
+        <v>688</v>
+      </c>
+      <c r="H7">
+        <f>MATCH(B4,B2:B7,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="89" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="87" t="s">
+        <v>687</v>
+      </c>
+      <c r="D9" s="87" t="s">
+        <v>577</v>
+      </c>
+      <c r="E9" s="87" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="25">
+        <v>1002</v>
+      </c>
+      <c r="D10" s="25">
+        <f>VLOOKUP(C10,B2:F7,MATCH("Sales",B2:F2,0),FALSE)</f>
+        <v>50000</v>
+      </c>
+      <c r="E10" s="88">
+        <f>VLOOKUP(C10,B2:F7,MATCH("Bonus Amount",B2:F2,0),FALSE)</f>
+        <v>2500</v>
+      </c>
+      <c r="G10" t="s">
+        <v>689</v>
+      </c>
+      <c r="H10">
+        <f>MATCH("Sales",B2:F2,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="86" t="s">
+        <v>691</v>
+      </c>
+      <c r="G12" t="s">
+        <v>688</v>
+      </c>
+      <c r="I12">
+        <f>MATCH(C15,B2:B7,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>689</v>
+      </c>
+      <c r="I13">
+        <f>MATCH("Sales",B2:F2,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="90" t="s">
+        <v>687</v>
+      </c>
+      <c r="D14" s="90" t="s">
+        <v>577</v>
+      </c>
+      <c r="E14" s="90" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="25">
+        <v>1004</v>
+      </c>
+      <c r="D15" s="25">
+        <f>INDEX(B2:F7,MATCH(C15,B2:B7,0),MATCH("Sales",B2:F2,0))</f>
+        <v>75000</v>
+      </c>
+      <c r="E15" s="25">
+        <f>INDEX(B2:F7,MATCH(C15,B2:B7,0),MATCH("Bonus Amount",B2:F2,0))</f>
+        <v>11250</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10" xr:uid="{A047E17B-A2CA-4FD8-92FF-2040F978D0C4}">
+      <formula1>$B$3:$B$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{D0E06332-745C-4019-A65E-6A1EF7168DF7}">
+      <formula1>$B$2:$B$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,22 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omsup\Documents\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFF2CC8-D5BE-42E2-801F-C051CD4465F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7EDBCD-2659-4504-9A3E-551BBC6AE1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="cond_formatting" sheetId="1" r:id="rId1"/>
-    <sheet name="Flashfill_custom_list" sheetId="3" r:id="rId2"/>
-    <sheet name="custom_list" sheetId="4" r:id="rId3"/>
-    <sheet name="custom_list_months" sheetId="5" r:id="rId4"/>
-    <sheet name="if_else" sheetId="7" r:id="rId5"/>
-    <sheet name="Advanced_functions" sheetId="8" r:id="rId6"/>
-    <sheet name="Sheet2" sheetId="9" r:id="rId7"/>
-    <sheet name="Lookup_func" sheetId="10" r:id="rId8"/>
+    <sheet name="Indirect" sheetId="12" r:id="rId1"/>
+    <sheet name="concat" sheetId="13" r:id="rId2"/>
+    <sheet name="cond_formatting" sheetId="1" r:id="rId3"/>
+    <sheet name="Flashfill_custom_list" sheetId="3" r:id="rId4"/>
+    <sheet name="custom_list" sheetId="4" r:id="rId5"/>
+    <sheet name="custom_list_months" sheetId="5" r:id="rId6"/>
+    <sheet name="if_else" sheetId="7" r:id="rId7"/>
+    <sheet name="Advanced_functions" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId9"/>
+    <sheet name="Lookup_func" sheetId="10" r:id="rId10"/>
+    <sheet name="hlookup" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet2!$C$15:$C$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Sheet2!$C$15:$C$24</definedName>
+    <definedName name="Apples">concat!$B$2:$B$6</definedName>
+    <definedName name="Bananas">concat!$C$2:$C$6</definedName>
+    <definedName name="Lemons">concat!$D$2:$D$6</definedName>
     <definedName name="orders">Table3[Order_ID]</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +46,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId12" roundtripDataChecksum="gT5L9Uh5Mkce+NjaHPxVAbIJlDW9RbqkjfO6mNdsl18="/>
     </ext>
   </extLst>
 </workbook>
@@ -69,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4722" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4773" uniqueCount="716">
   <si>
     <t>Region</t>
   </si>
@@ -2148,6 +2154,75 @@
   </si>
   <si>
     <t>index-match</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>using vlookup</t>
+  </si>
+  <si>
+    <t>using index-match</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>R2C1</t>
+  </si>
+  <si>
+    <t>R1C1 Style</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Sunil</t>
+  </si>
+  <si>
+    <t>Bananas</t>
+  </si>
+  <si>
+    <t>Lemons</t>
+  </si>
+  <si>
+    <t>Fruit:</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>using xlookup</t>
   </si>
 </sst>
 </file>
@@ -2159,11 +2234,18 @@
     <numFmt numFmtId="165" formatCode="[$INR]\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$₹-439]#,##0.00"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2314,7 +2396,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2378,6 +2460,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2585,105 +2673,106 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="10" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="15" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="15" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="15" fillId="7" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="16" fillId="8" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="16" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="16" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="16" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="16" fillId="7" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="17" fillId="8" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="8" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="8" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2692,71 +2781,68 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2765,17 +2851,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="40% - Accent4" xfId="3" builtinId="43"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{88D63144-27FB-4D9D-A79B-725FA5FE3C0E}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="45">
@@ -4097,6 +4190,679 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D81F403-80D2-451A-BE2B-A0BA740AF252}">
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="5" width="8.88671875" style="91"/>
+    <col min="6" max="6" width="11.5546875" style="91" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="91"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="91">
+        <v>111</v>
+      </c>
+      <c r="C1" s="91" t="s">
+        <v>703</v>
+      </c>
+      <c r="D1" s="91" cm="1">
+        <f t="array" aca="1" ref="D1" ca="1">INDIRECT(C1)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="91">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="91">
+        <v>333</v>
+      </c>
+      <c r="C3" s="91" t="s">
+        <v>704</v>
+      </c>
+      <c r="D3" s="91" cm="1">
+        <f t="array" aca="1" ref="D3" ca="1">INDIRECT(C3,FALSE)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E4" s="91">
+        <v>4</v>
+      </c>
+      <c r="F4" s="91" t="s">
+        <v>702</v>
+      </c>
+      <c r="H4" s="91" cm="1">
+        <f t="array" aca="1" ref="H4" ca="1">INDIRECT(F4)+100</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="92" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="92" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D12" s="91" t="s">
+        <v>583</v>
+      </c>
+      <c r="E12" s="91" t="s">
+        <v>549</v>
+      </c>
+      <c r="F12" s="91" t="str">
+        <f>D12&amp;"   "&amp;E12</f>
+        <v>Ankit   Sharma</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FCD3B0-4BC8-4681-8037-4E058512B5F9}">
+  <dimension ref="B1:J19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="85" t="s">
+        <v>686</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>600</v>
+      </c>
+      <c r="D2" s="85" t="s">
+        <v>577</v>
+      </c>
+      <c r="E2" s="85" t="s">
+        <v>624</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B3" s="25">
+        <v>1001</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>604</v>
+      </c>
+      <c r="D3" s="25">
+        <v>70000</v>
+      </c>
+      <c r="E3" s="84">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="25">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="25">
+        <v>1002</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>605</v>
+      </c>
+      <c r="D4" s="25">
+        <v>50000</v>
+      </c>
+      <c r="E4" s="84">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="25">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="25">
+        <v>1003</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>606</v>
+      </c>
+      <c r="D5" s="25">
+        <v>45000</v>
+      </c>
+      <c r="E5" s="84">
+        <v>0</v>
+      </c>
+      <c r="F5" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="25">
+        <v>1004</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="D6" s="25">
+        <v>75000</v>
+      </c>
+      <c r="E6" s="84">
+        <v>0.15</v>
+      </c>
+      <c r="F6" s="25">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="25">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>623</v>
+      </c>
+      <c r="D7" s="25">
+        <v>55000</v>
+      </c>
+      <c r="E7" s="84">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="25">
+        <v>2750</v>
+      </c>
+      <c r="G7" t="s">
+        <v>688</v>
+      </c>
+      <c r="H7">
+        <f>MATCH(B4,B2:B7,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="88" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="86" t="s">
+        <v>687</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>577</v>
+      </c>
+      <c r="E9" s="86" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="25">
+        <v>1002</v>
+      </c>
+      <c r="D10" s="25">
+        <f>VLOOKUP(C10,B2:F7,MATCH("Sales",B2:F2,0),FALSE)</f>
+        <v>50000</v>
+      </c>
+      <c r="E10" s="87">
+        <f>VLOOKUP(C10,B2:F7,MATCH("Bonus Amount",B2:F2,0),FALSE)</f>
+        <v>2500</v>
+      </c>
+      <c r="G10" t="s">
+        <v>689</v>
+      </c>
+      <c r="H10">
+        <f>MATCH("Sales",B2:F2,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="52" t="s">
+        <v>691</v>
+      </c>
+      <c r="G12" t="s">
+        <v>688</v>
+      </c>
+      <c r="I12">
+        <f>MATCH(C15,B2:B7,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="G13" t="s">
+        <v>689</v>
+      </c>
+      <c r="I13">
+        <f>MATCH("Sales",B2:F2,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="89" t="s">
+        <v>687</v>
+      </c>
+      <c r="D14" s="89" t="s">
+        <v>577</v>
+      </c>
+      <c r="E14" s="89" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="25">
+        <v>1004</v>
+      </c>
+      <c r="D15" s="25">
+        <f>INDEX(B2:F7,MATCH(C15,B2:B7,0),MATCH("Sales",B2:F2,0))</f>
+        <v>75000</v>
+      </c>
+      <c r="E15" s="25">
+        <f>INDEX(B2:F7,MATCH(C15,B2:B7,0),MATCH("Bonus Amount",B2:F2,0))</f>
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C18" s="89" t="s">
+        <v>687</v>
+      </c>
+      <c r="D18" s="89" t="s">
+        <v>577</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C19" s="25">
+        <v>1004</v>
+      </c>
+      <c r="D19" s="25">
+        <f>_xlfn.XLOOKUP(C19,$B$3:$B$7,$D$3:$D$7)</f>
+        <v>75000</v>
+      </c>
+      <c r="E19" s="25">
+        <f>_xlfn.XLOOKUP(C19,$B$3:$B$7,$F$3:$F$7)</f>
+        <v>11250</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10" xr:uid="{A047E17B-A2CA-4FD8-92FF-2040F978D0C4}">
+      <formula1>$B$3:$B$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15 C19" xr:uid="{D0E06332-745C-4019-A65E-6A1EF7168DF7}">
+      <formula1>$B$2:$B$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CBEC3E4-77E5-4A66-A09B-D9FF6175E7CC}">
+  <dimension ref="A3:H20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26" t="s">
+        <v>693</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>694</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>695</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>696</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
+        <v>697</v>
+      </c>
+      <c r="B4" s="25">
+        <v>100</v>
+      </c>
+      <c r="C4" s="25">
+        <v>585</v>
+      </c>
+      <c r="D4" s="25">
+        <v>333</v>
+      </c>
+      <c r="E4" s="25">
+        <v>745</v>
+      </c>
+      <c r="F4" s="25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
+        <v>698</v>
+      </c>
+      <c r="B5" s="25">
+        <v>100</v>
+      </c>
+      <c r="C5" s="25">
+        <v>500</v>
+      </c>
+      <c r="D5" s="25">
+        <v>600</v>
+      </c>
+      <c r="E5" s="25">
+        <v>700</v>
+      </c>
+      <c r="F5" s="25">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>577</v>
+      </c>
+      <c r="B6" s="25">
+        <v>2000</v>
+      </c>
+      <c r="C6" s="25">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="25">
+        <v>8000</v>
+      </c>
+      <c r="E6" s="25">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="25">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
+        <v>699</v>
+      </c>
+      <c r="B7" s="25">
+        <v>400</v>
+      </c>
+      <c r="C7" s="25">
+        <v>500</v>
+      </c>
+      <c r="D7" s="25">
+        <v>300</v>
+      </c>
+      <c r="E7" s="25">
+        <v>300</v>
+      </c>
+      <c r="F7" s="25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F9" s="90" t="s">
+        <v>700</v>
+      </c>
+      <c r="G9" s="90"/>
+      <c r="H9">
+        <f>MATCH(C10,A3:F3,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="90" t="s">
+        <v>586</v>
+      </c>
+      <c r="C10" s="90" t="s">
+        <v>693</v>
+      </c>
+      <c r="F10" s="90" t="s">
+        <v>586</v>
+      </c>
+      <c r="G10" s="90" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="90" t="s">
+        <v>577</v>
+      </c>
+      <c r="C11" s="28">
+        <f>HLOOKUP($C$10,$A$3:$F$7,MATCH(B11,$A$3:$A$7,0),FALSE)</f>
+        <v>2000</v>
+      </c>
+      <c r="F11" s="90" t="s">
+        <v>577</v>
+      </c>
+      <c r="G11" s="28">
+        <f>VLOOKUP(F11,$A$3:$F$7,MATCH($G$10,$A$3:$F$3,0),FALSE)</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="90" t="s">
+        <v>698</v>
+      </c>
+      <c r="C12" s="28">
+        <f>HLOOKUP($C$10,$A$3:$F$7,MATCH(B12,$A$3:$A$7,0),FALSE)</f>
+        <v>100</v>
+      </c>
+      <c r="F12" s="90" t="s">
+        <v>699</v>
+      </c>
+      <c r="G12" s="28">
+        <f>VLOOKUP(F12,$A$3:$F$7,MATCH($G$10,$A$3:$F$3,0),FALSE)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="90" t="s">
+        <v>699</v>
+      </c>
+      <c r="C13" s="28">
+        <f>HLOOKUP($C$10,$A$3:$F$7,MATCH(B13,$A$3:$A$7,0),FALSE)</f>
+        <v>400</v>
+      </c>
+      <c r="F13" s="90" t="s">
+        <v>697</v>
+      </c>
+      <c r="G13" s="28">
+        <f>VLOOKUP(F13,$A$3:$F$7,MATCH($G$10,$A$3:$F$3,0),FALSE)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F16" s="90" t="s">
+        <v>701</v>
+      </c>
+      <c r="G16" s="90"/>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F17" s="90" t="s">
+        <v>586</v>
+      </c>
+      <c r="G17" s="90" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="18" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F18" s="90" t="s">
+        <v>577</v>
+      </c>
+      <c r="G18" s="28"/>
+    </row>
+    <row r="19" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F19" s="90" t="s">
+        <v>699</v>
+      </c>
+      <c r="G19" s="28"/>
+    </row>
+    <row r="20" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F20" s="90" t="s">
+        <v>697</v>
+      </c>
+      <c r="G20" s="28"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 G10 G17" xr:uid="{65F6DE29-6950-4D2F-B0EB-D3A0B82AC2CC}">
+      <formula1>$B$3:$F$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A088EC8-1CAB-4CC3-96BB-F72ABE6822D1}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="28"/>
+      <c r="B1" s="93" t="s">
+        <v>650</v>
+      </c>
+      <c r="C1" s="93" t="s">
+        <v>709</v>
+      </c>
+      <c r="D1" s="93" t="s">
+        <v>710</v>
+      </c>
+      <c r="F1" s="95" t="s">
+        <v>711</v>
+      </c>
+      <c r="G1" s="95" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="94" t="s">
+        <v>707</v>
+      </c>
+      <c r="B2" s="28">
+        <v>55</v>
+      </c>
+      <c r="C2" s="28">
+        <v>44</v>
+      </c>
+      <c r="D2" s="28">
+        <v>44</v>
+      </c>
+      <c r="F2" s="94" t="s">
+        <v>621</v>
+      </c>
+      <c r="G2" s="94">
+        <v>242</v>
+      </c>
+      <c r="H2">
+        <f>SUM(Lemons)</f>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="94" t="s">
+        <v>584</v>
+      </c>
+      <c r="B3" s="28">
+        <v>33</v>
+      </c>
+      <c r="C3" s="28">
+        <v>32</v>
+      </c>
+      <c r="D3" s="28">
+        <v>66</v>
+      </c>
+      <c r="F3" s="94" t="s">
+        <v>712</v>
+      </c>
+      <c r="G3" s="94">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="94" t="s">
+        <v>582</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45</v>
+      </c>
+      <c r="C4" s="28">
+        <v>50</v>
+      </c>
+      <c r="D4" s="28">
+        <v>44</v>
+      </c>
+      <c r="F4" s="94" t="s">
+        <v>713</v>
+      </c>
+      <c r="G4" s="94">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="94" t="s">
+        <v>708</v>
+      </c>
+      <c r="B5" s="28">
+        <v>34</v>
+      </c>
+      <c r="C5" s="28">
+        <v>32</v>
+      </c>
+      <c r="D5" s="28">
+        <v>22</v>
+      </c>
+      <c r="F5" s="94" t="s">
+        <v>714</v>
+      </c>
+      <c r="G5" s="94">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="94" t="s">
+        <v>585</v>
+      </c>
+      <c r="B6" s="28">
+        <v>21</v>
+      </c>
+      <c r="C6" s="28">
+        <v>26</v>
+      </c>
+      <c r="D6" s="28">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -50226,7 +50992,7 @@
       <c r="X1000" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G1:G1048576">
     <cfRule type="colorScale" priority="10">
       <colorScale>
@@ -50260,7 +51026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D1199D8-C254-48C0-AC5F-ADDEC91F4A49}">
   <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -50492,7 +51258,7 @@
       <c r="L26" s="37"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{AFE13D69-7C3F-4364-A764-94BD20E9F59C}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{D4312324-D04C-4765-8A3B-1506DE463DAC}"/>
@@ -50503,7 +51269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD2C2FD5-8379-4925-B2E3-1BBDDF1E9A2D}">
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -50584,12 +51350,12 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9ADD8E7-B498-4D82-A60B-0B043A12DAA9}">
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -50908,7 +51674,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B9">
     <sortCondition ref="A2:A9" customList="January,February,March,April,May,June,July,August,September,October,November,December"/>
   </sortState>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="B1:B9">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>20000</formula>
@@ -50921,7 +51687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245A1291-890C-4E69-BBCE-61FD758841BF}">
   <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -51315,7 +52081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6891C419-E3F4-4F78-B82D-457603678086}">
   <dimension ref="C2:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -51379,7 +52145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24C003C-206A-4005-AB81-1F886CB6485B}">
   <dimension ref="B3:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -51564,226 +52330,4 @@
   <autoFilter ref="C15:C24" xr:uid="{F24C003C-206A-4005-AB81-1F886CB6485B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FCD3B0-4BC8-4681-8037-4E058512B5F9}">
-  <dimension ref="B1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="J1" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="85" t="s">
-        <v>686</v>
-      </c>
-      <c r="C2" s="85" t="s">
-        <v>600</v>
-      </c>
-      <c r="D2" s="85" t="s">
-        <v>577</v>
-      </c>
-      <c r="E2" s="85" t="s">
-        <v>624</v>
-      </c>
-      <c r="F2" s="85" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="25">
-        <v>1001</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>604</v>
-      </c>
-      <c r="D3" s="25">
-        <v>70000</v>
-      </c>
-      <c r="E3" s="84">
-        <v>0.1</v>
-      </c>
-      <c r="F3" s="25">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="25">
-        <v>1002</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>605</v>
-      </c>
-      <c r="D4" s="25">
-        <v>50000</v>
-      </c>
-      <c r="E4" s="84">
-        <v>0.05</v>
-      </c>
-      <c r="F4" s="25">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="25">
-        <v>1003</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>606</v>
-      </c>
-      <c r="D5" s="25">
-        <v>45000</v>
-      </c>
-      <c r="E5" s="84">
-        <v>0</v>
-      </c>
-      <c r="F5" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="25">
-        <v>1004</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>607</v>
-      </c>
-      <c r="D6" s="25">
-        <v>75000</v>
-      </c>
-      <c r="E6" s="84">
-        <v>0.15</v>
-      </c>
-      <c r="F6" s="25">
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="25">
-        <v>1005</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>623</v>
-      </c>
-      <c r="D7" s="25">
-        <v>55000</v>
-      </c>
-      <c r="E7" s="84">
-        <v>0.05</v>
-      </c>
-      <c r="F7" s="25">
-        <v>2750</v>
-      </c>
-      <c r="G7" t="s">
-        <v>688</v>
-      </c>
-      <c r="H7">
-        <f>MATCH(B4,B2:B7,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="89" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="87" t="s">
-        <v>687</v>
-      </c>
-      <c r="D9" s="87" t="s">
-        <v>577</v>
-      </c>
-      <c r="E9" s="87" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C10" s="25">
-        <v>1002</v>
-      </c>
-      <c r="D10" s="25">
-        <f>VLOOKUP(C10,B2:F7,MATCH("Sales",B2:F2,0),FALSE)</f>
-        <v>50000</v>
-      </c>
-      <c r="E10" s="88">
-        <f>VLOOKUP(C10,B2:F7,MATCH("Bonus Amount",B2:F2,0),FALSE)</f>
-        <v>2500</v>
-      </c>
-      <c r="G10" t="s">
-        <v>689</v>
-      </c>
-      <c r="H10">
-        <f>MATCH("Sales",B2:F2,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="G11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="86" t="s">
-        <v>691</v>
-      </c>
-      <c r="G12" t="s">
-        <v>688</v>
-      </c>
-      <c r="I12">
-        <f>MATCH(C15,B2:B7,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="G13" t="s">
-        <v>689</v>
-      </c>
-      <c r="I13">
-        <f>MATCH("Sales",B2:F2,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C14" s="90" t="s">
-        <v>687</v>
-      </c>
-      <c r="D14" s="90" t="s">
-        <v>577</v>
-      </c>
-      <c r="E14" s="90" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="25">
-        <v>1004</v>
-      </c>
-      <c r="D15" s="25">
-        <f>INDEX(B2:F7,MATCH(C15,B2:B7,0),MATCH("Sales",B2:F2,0))</f>
-        <v>75000</v>
-      </c>
-      <c r="E15" s="25">
-        <f>INDEX(B2:F7,MATCH(C15,B2:B7,0),MATCH("Bonus Amount",B2:F2,0))</f>
-        <v>11250</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10" xr:uid="{A047E17B-A2CA-4FD8-92FF-2040F978D0C4}">
-      <formula1>$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{D0E06332-745C-4019-A65E-6A1EF7168DF7}">
-      <formula1>$B$2:$B$7</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart_Cleaning_Structuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omsup\Documents\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4E6E20-F007-470F-97C9-42C96063DE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741C6FD7-008F-456F-A1DE-624684545577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indirect" sheetId="12" r:id="rId1"/>
@@ -2255,7 +2255,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="[$INR]\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$₹-439]#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="167" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -2722,7 +2722,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2917,19 +2917,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="40% - Accent4" xfId="3" builtinId="43"/>
@@ -2975,14 +2976,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3957,6 +3950,14 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color rgb="FF000000"/>
@@ -4030,29 +4031,29 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{28BA5535-5788-4AB1-921A-039F14F54D15}" name="dmart_sales" displayName="dmart_sales" ref="A1:R500" totalsRowCount="1" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
   <autoFilter ref="A1:R499" xr:uid="{28BA5535-5788-4AB1-921A-039F14F54D15}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R499">
-    <sortCondition sortBy="cellColor" ref="E1:E499" dxfId="5"/>
+    <sortCondition sortBy="cellColor" ref="E1:E499" dxfId="41"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{65E6CC84-6F4C-44CA-9C99-120FD23566F9}" name="Order_ID" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{95D805C7-3A69-4431-813C-AED81C05B129}" name="Region" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="17" xr3:uid="{4891D56D-8ABF-4FA3-B907-382919F05DFB}" name="Updated_Region" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{AD731D64-0C98-4E2C-8C7E-DA1C59744960}" name="Category" totalsRowLabel="total sales" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{E3DB0743-D046-45B3-B885-2F62C83EF45F}" name="sales" totalsRowFunction="sum" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="16" xr3:uid="{A17DAFFE-BE88-46AE-92E8-5070A02CD175}" name="sales_category" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="1" xr3:uid="{65E6CC84-6F4C-44CA-9C99-120FD23566F9}" name="Order_ID" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{95D805C7-3A69-4431-813C-AED81C05B129}" name="Region" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="17" xr3:uid="{4891D56D-8ABF-4FA3-B907-382919F05DFB}" name="Updated_Region" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{AD731D64-0C98-4E2C-8C7E-DA1C59744960}" name="Category" totalsRowLabel="total sales" dataDxfId="34" totalsRowDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{E3DB0743-D046-45B3-B885-2F62C83EF45F}" name="sales" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{A17DAFFE-BE88-46AE-92E8-5070A02CD175}" name="sales_category" dataDxfId="30" totalsRowDxfId="29">
       <calculatedColumnFormula>IF(dmart_sales[[#This Row],[sales]]&gt;3000,"High Sales",IF(dmart_sales[[#This Row],[sales]]&gt;1000,"Medium Sales",IF(dmart_sales[[#This Row],[sales]]&lt;1000,"Low Sales")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{764C9B79-25BD-4E91-84F1-EF01A46B6CE6}" name="discount" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{8A685D1E-193F-4B06-AEEC-D7B5707356CB}" name="quantity" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{AA2D0404-3A02-492B-A7F9-FB21C0D90029}" name="order_date" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="8" xr3:uid="{B84E34D0-E873-4CB7-855D-B95A06454F09}" name="delivery_date" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{02F2D684-13B5-466E-9E84-259BC9E24A6E}" name="Column1" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{67E60644-68E7-461D-89FD-19FEDFE92E33}" name="customer_type" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{DE3BFD9A-B1E4-466F-ABF6-89CAE2992356}" name="customer_type2" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{B560B7F1-8234-4E8A-A0B3-6FAA6B4550A0}" name="payment_mode" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{DB9E1769-0689-4C49-95C9-88E2EF737695}" name="profit" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{C8C418C5-247E-47D9-A677-4A5BAF3FB5B7}" name="city" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{902D2CA8-6521-4B0D-B616-7AFBC6823689}" name="updated_city" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{52801663-005F-401D-B9DE-7B6472E40B55}" name="Discount_category" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="5" xr3:uid="{764C9B79-25BD-4E91-84F1-EF01A46B6CE6}" name="discount" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{8A685D1E-193F-4B06-AEEC-D7B5707356CB}" name="quantity" dataDxfId="26" totalsRowDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{AA2D0404-3A02-492B-A7F9-FB21C0D90029}" name="order_date" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{B84E34D0-E873-4CB7-855D-B95A06454F09}" name="delivery_date" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{02F2D684-13B5-466E-9E84-259BC9E24A6E}" name="Column1" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{67E60644-68E7-461D-89FD-19FEDFE92E33}" name="customer_type" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{DE3BFD9A-B1E4-466F-ABF6-89CAE2992356}" name="customer_type2" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{B560B7F1-8234-4E8A-A0B3-6FAA6B4550A0}" name="payment_mode" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{DB9E1769-0689-4C49-95C9-88E2EF737695}" name="profit" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{C8C418C5-247E-47D9-A677-4A5BAF3FB5B7}" name="city" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{902D2CA8-6521-4B0D-B616-7AFBC6823689}" name="updated_city" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{52801663-005F-401D-B9DE-7B6472E40B55}" name="Discount_category" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>IF(AND(dmart_sales[[#This Row],[customer_type2]]="Member",OR(dmart_sales[[#This Row],[payment_mode]]="UPI",dmart_sales[[#This Row],[payment_mode]]="Card")),"yes","no")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4805,15 +4806,16 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823AFEE9-D9AC-439E-9D3E-9033F748D023}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="10.44140625" style="104" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="99"/>
     <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="82" t="s">
         <v>716</v>
       </c>
@@ -4831,7 +4833,7 @@
       </c>
       <c r="F1" s="97"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="22">
         <v>21</v>
       </c>
@@ -4848,7 +4850,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="22">
         <v>18</v>
       </c>
@@ -4858,12 +4860,18 @@
       <c r="C3" s="22">
         <v>10</v>
       </c>
-      <c r="D3" s="103"/>
+      <c r="D3" s="103">
+        <v>46358</v>
+      </c>
       <c r="E3" s="64">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <f>MONTH(D3)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="22">
         <v>60</v>
       </c>
@@ -4873,12 +4881,17 @@
       <c r="C4" s="22">
         <v>6</v>
       </c>
-      <c r="D4" s="103"/>
+      <c r="D4" s="103">
+        <v>46298</v>
+      </c>
       <c r="E4" s="64">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="107">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="22">
         <v>78</v>
       </c>
@@ -4888,7 +4901,9 @@
       <c r="C5" s="22">
         <v>9</v>
       </c>
-      <c r="D5" s="103"/>
+      <c r="D5" s="103">
+        <v>46305</v>
+      </c>
       <c r="E5" s="64">
         <v>45</v>
       </c>
@@ -4896,14 +4911,14 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H6" t="b">
         <f>AND(E2&gt;40,E2&lt;=75)</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="5">
     <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Age Error" error="The age entered is not within range" promptTitle="Age Restrictions" prompt="Enter age between 18 to 60" sqref="A1:A1048576" xr:uid="{6B5B23E9-E7AC-4AF4-A99F-02872153FFC6}">
       <formula1>18</formula1>
       <formula2>60</formula2>
@@ -4912,16 +4927,15 @@
       <formula1>$G$2</formula1>
       <formula2>$G$3</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date Range" error="Your date is not within range" promptTitle="Date Range " prompt="Date must be after 10-02-26" sqref="D8:D1048576 D3 D4:D5 D2" xr:uid="{6965CDE0-9CB3-4DA2-865A-C561F2674246}">
-      <formula1>46297</formula1>
-    </dataValidation>
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid OTP" error="Pls enter valid range of OTP" promptTitle="OTP" prompt="OPT is always of 4 characters" sqref="B1:B1048576" xr:uid="{CAF73843-5633-4563-AEAA-67A16830D222}">
       <formula1>4</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{DEC47AAE-ECF3-4BEE-92B6-D834DF05AD5A}">
       <formula1>AND(E1&gt;40,E1&lt;=75)</formula1>
     </dataValidation>
-    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Date Range" error="Your date is not within range" promptTitle="Date Range " prompt="Date must be after 10-02-26" sqref="D1" xr:uid="{375F414D-F5B2-486D-9E3B-5FEA6BFFAE6B}"/>
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Date" error="Pls enter valid date" promptTitle="Date Range" prompt="Enter the date after 10-02-2026" sqref="D1:D1048576" xr:uid="{4A82C91D-92AE-48BB-963B-77CFB1E56421}">
+      <formula1>46297</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
